--- a/research/traditional_assets/database/data/luxembourg/luxembourg_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_heathcare_information_and_technology.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09663661468084669</v>
+        <v>0.09642937996383265</v>
       </c>
       <c r="C2">
-        <v>12269.43038347135</v>
+        <v>12181.95836302008</v>
       </c>
       <c r="D2">
-        <v>11539.53038347135</v>
+        <v>11586.7636562312</v>
       </c>
       <c r="E2">
-        <v>-3804.129321111863</v>
+        <v>-3669.424027900744</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>134.7052932111186</v>
       </c>
       <c r="G2">
         <v>729.9</v>
@@ -1457,28 +1457,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.775676248519266</v>
       </c>
       <c r="N2">
-        <v>830.3200000000001</v>
+        <v>823.5443237514808</v>
       </c>
       <c r="O2">
-        <v>207.081808</v>
+        <v>205.3919543436193</v>
       </c>
       <c r="P2">
-        <v>623.238192</v>
+        <v>618.1523694078614</v>
       </c>
       <c r="Q2">
-        <v>1200.338192</v>
+        <v>1195.252369407861</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09663661468084669</v>
+        <v>0.09702204865033601</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.182957243656721</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>122.5442257784166</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09642937996383265</v>
+        <v>0.09622214524681862</v>
       </c>
       <c r="C3">
-        <v>12181.95836302008</v>
+        <v>12094.87459950893</v>
       </c>
       <c r="D3">
-        <v>11586.7636562312</v>
+        <v>11634.38518593117</v>
       </c>
       <c r="E3">
-        <v>-3669.424027900744</v>
+        <v>-3534.718734689625</v>
       </c>
       <c r="F3">
-        <v>134.7052932111186</v>
+        <v>269.4105864222373</v>
       </c>
       <c r="G3">
         <v>729.9</v>
@@ -1539,28 +1539,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M3">
-        <v>6.775676248519266</v>
+        <v>13.55135249703853</v>
       </c>
       <c r="N3">
-        <v>823.5443237514808</v>
+        <v>816.7686475029615</v>
       </c>
       <c r="O3">
-        <v>205.3919543436193</v>
+        <v>203.7021006872386</v>
       </c>
       <c r="P3">
-        <v>618.1523694078614</v>
+        <v>613.0665468157229</v>
       </c>
       <c r="Q3">
-        <v>1195.252369407861</v>
+        <v>1190.166546815723</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09702204865033601</v>
+        <v>0.09741534861920267</v>
       </c>
       <c r="T3">
-        <v>1.182957243656721</v>
+        <v>1.192040383815304</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>122.5442257784166</v>
+        <v>61.27211288920832</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09622214524681862</v>
+        <v>0.09601491052980458</v>
       </c>
       <c r="C4">
-        <v>12094.87459950893</v>
+        <v>12008.18389989561</v>
       </c>
       <c r="D4">
-        <v>11634.38518593117</v>
+        <v>11682.39977952897</v>
       </c>
       <c r="E4">
-        <v>-3534.718734689625</v>
+        <v>-3400.013441478507</v>
       </c>
       <c r="F4">
-        <v>269.4105864222373</v>
+        <v>404.1158796333559</v>
       </c>
       <c r="G4">
         <v>729.9</v>
@@ -1621,28 +1621,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M4">
-        <v>13.55135249703853</v>
+        <v>20.3270287455578</v>
       </c>
       <c r="N4">
-        <v>816.7686475029615</v>
+        <v>809.9929712544423</v>
       </c>
       <c r="O4">
-        <v>203.7021006872386</v>
+        <v>202.0122470308579</v>
       </c>
       <c r="P4">
-        <v>613.0665468157229</v>
+        <v>607.9807242235844</v>
       </c>
       <c r="Q4">
-        <v>1190.166546815723</v>
+        <v>1185.080724223584</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09741534861920267</v>
+        <v>0.09781675786577793</v>
       </c>
       <c r="T4">
-        <v>1.192040383815304</v>
+        <v>1.201310805214271</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>61.27211288920832</v>
+        <v>40.84807525947222</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09601491052980458</v>
+        <v>0.09580767581279055</v>
       </c>
       <c r="C5">
-        <v>12008.18389989561</v>
+        <v>11921.89115081909</v>
       </c>
       <c r="D5">
-        <v>11682.39977952897</v>
+        <v>11730.81232366357</v>
       </c>
       <c r="E5">
-        <v>-3400.013441478507</v>
+        <v>-3265.308148267388</v>
       </c>
       <c r="F5">
-        <v>404.1158796333559</v>
+        <v>538.8211728444745</v>
       </c>
       <c r="G5">
         <v>729.9</v>
@@ -1703,28 +1703,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M5">
-        <v>20.3270287455578</v>
+        <v>27.10270499407707</v>
       </c>
       <c r="N5">
-        <v>809.9929712544423</v>
+        <v>803.217295005923</v>
       </c>
       <c r="O5">
-        <v>202.0122470308579</v>
+        <v>200.3223933744772</v>
       </c>
       <c r="P5">
-        <v>607.9807242235844</v>
+        <v>602.8949016314458</v>
       </c>
       <c r="Q5">
-        <v>1185.080724223584</v>
+        <v>1179.994901631446</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09781675786577793</v>
+        <v>0.09822652980499016</v>
       </c>
       <c r="T5">
-        <v>1.201310805214271</v>
+        <v>1.210774360392383</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.84807525947222</v>
+        <v>30.63605644460416</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09580767581279055</v>
+        <v>0.09560044109577652</v>
       </c>
       <c r="C6">
-        <v>11921.89115081909</v>
+        <v>11836.00132025747</v>
       </c>
       <c r="D6">
-        <v>11730.81232366357</v>
+        <v>11779.62778631306</v>
       </c>
       <c r="E6">
-        <v>-3265.308148267388</v>
+        <v>-3130.60285505627</v>
       </c>
       <c r="F6">
-        <v>538.8211728444745</v>
+        <v>673.5264660555931</v>
       </c>
       <c r="G6">
         <v>729.9</v>
@@ -1785,28 +1785,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M6">
-        <v>27.10270499407707</v>
+        <v>33.87838124259633</v>
       </c>
       <c r="N6">
-        <v>803.217295005923</v>
+        <v>796.4416187574037</v>
       </c>
       <c r="O6">
-        <v>200.3223933744772</v>
+        <v>198.6325397180965</v>
       </c>
       <c r="P6">
-        <v>602.8949016314458</v>
+        <v>597.8090790393072</v>
       </c>
       <c r="Q6">
-        <v>1179.994901631446</v>
+        <v>1174.909079039307</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09822652980499016</v>
+        <v>0.09864492852187003</v>
       </c>
       <c r="T6">
-        <v>1.210774360392383</v>
+        <v>1.220437148311086</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.63605644460416</v>
+        <v>24.50884515568333</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09560044109577652</v>
+        <v>0.09539320637876249</v>
       </c>
       <c r="C7">
-        <v>11836.00132025747</v>
+        <v>11750.51945922743</v>
       </c>
       <c r="D7">
-        <v>11779.62778631306</v>
+        <v>11828.85121849414</v>
       </c>
       <c r="E7">
-        <v>-3130.60285505627</v>
+        <v>-2995.897561845151</v>
       </c>
       <c r="F7">
-        <v>673.5264660555931</v>
+        <v>808.2317592667118</v>
       </c>
       <c r="G7">
         <v>729.9</v>
@@ -1867,28 +1867,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M7">
-        <v>33.87838124259633</v>
+        <v>40.6540574911156</v>
       </c>
       <c r="N7">
-        <v>796.4416187574037</v>
+        <v>789.6659425088844</v>
       </c>
       <c r="O7">
-        <v>198.6325397180965</v>
+        <v>196.9426860617158</v>
       </c>
       <c r="P7">
-        <v>597.8090790393072</v>
+        <v>592.7232564471686</v>
       </c>
       <c r="Q7">
-        <v>1174.909079039307</v>
+        <v>1169.823256447169</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09864492852187003</v>
+        <v>0.09907222933910903</v>
       </c>
       <c r="T7">
-        <v>1.220437148311086</v>
+        <v>1.230305527462102</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.50884515568333</v>
+        <v>20.42403762973611</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09539320637876249</v>
+        <v>0.09518597166174847</v>
       </c>
       <c r="C8">
-        <v>11750.51945922743</v>
+        <v>11665.4507035265</v>
       </c>
       <c r="D8">
-        <v>11828.85121849414</v>
+        <v>11878.48775600433</v>
       </c>
       <c r="E8">
-        <v>-2995.897561845151</v>
+        <v>-2861.192268634032</v>
       </c>
       <c r="F8">
-        <v>808.2317592667117</v>
+        <v>942.9370524778303</v>
       </c>
       <c r="G8">
         <v>729.9</v>
@@ -1949,28 +1949,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M8">
-        <v>40.65405749111559</v>
+        <v>47.42973373963486</v>
       </c>
       <c r="N8">
-        <v>789.6659425088844</v>
+        <v>782.8902662603651</v>
       </c>
       <c r="O8">
-        <v>196.9426860617158</v>
+        <v>195.2528324053351</v>
       </c>
       <c r="P8">
-        <v>592.7232564471686</v>
+        <v>587.6374338550301</v>
       </c>
       <c r="Q8">
-        <v>1169.823256447169</v>
+        <v>1164.73743385503</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09907222933910903</v>
+        <v>0.0995087194212349</v>
       </c>
       <c r="T8">
-        <v>1.230305527462102</v>
+        <v>1.240386129820668</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.42403762973611</v>
+        <v>17.50631796834524</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09518597166174846</v>
+        <v>0.09497873694473444</v>
       </c>
       <c r="C9">
-        <v>11665.4507035265</v>
+        <v>11580.80027551935</v>
       </c>
       <c r="D9">
-        <v>11878.48775600433</v>
+        <v>11928.5426212083</v>
       </c>
       <c r="E9">
-        <v>-2861.192268634032</v>
+        <v>-2726.486975422914</v>
       </c>
       <c r="F9">
-        <v>942.9370524778304</v>
+        <v>1077.642345688949</v>
       </c>
       <c r="G9">
         <v>729.9</v>
@@ -2031,28 +2031,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M9">
-        <v>47.42973373963487</v>
+        <v>54.20540998815413</v>
       </c>
       <c r="N9">
-        <v>782.8902662603651</v>
+        <v>776.114590011846</v>
       </c>
       <c r="O9">
-        <v>195.2528324053351</v>
+        <v>193.5629787489544</v>
       </c>
       <c r="P9">
-        <v>587.6374338550301</v>
+        <v>582.5516112628916</v>
       </c>
       <c r="Q9">
-        <v>1164.73743385503</v>
+        <v>1159.651611262891</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0995087194212349</v>
+        <v>0.0999546984181896</v>
       </c>
       <c r="T9">
-        <v>1.240386129820668</v>
+        <v>1.250685875708767</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.50631796834523</v>
+        <v>15.31802822230208</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09497873694473444</v>
+        <v>0.09477150222772041</v>
       </c>
       <c r="C10">
-        <v>11580.80027551935</v>
+        <v>11496.57348596942</v>
       </c>
       <c r="D10">
-        <v>11928.5426212083</v>
+        <v>11979.02112486949</v>
       </c>
       <c r="E10">
-        <v>-2726.486975422914</v>
+        <v>-2591.781682211795</v>
       </c>
       <c r="F10">
-        <v>1077.642345688949</v>
+        <v>1212.347638900068</v>
       </c>
       <c r="G10">
         <v>729.9</v>
@@ -2113,28 +2113,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M10">
-        <v>54.20540998815413</v>
+        <v>60.98108623667339</v>
       </c>
       <c r="N10">
-        <v>776.114590011846</v>
+        <v>769.3389137633267</v>
       </c>
       <c r="O10">
-        <v>193.5629787489544</v>
+        <v>191.8731250925737</v>
       </c>
       <c r="P10">
-        <v>582.5516112628916</v>
+        <v>577.465788670753</v>
       </c>
       <c r="Q10">
-        <v>1159.651611262891</v>
+        <v>1154.565788670753</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0999546984181896</v>
+        <v>0.1004104791513411</v>
       </c>
       <c r="T10">
-        <v>1.250685875708767</v>
+        <v>1.261211989638363</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.31802822230208</v>
+        <v>13.61602508649074</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09477150222772041</v>
+        <v>0.09456426751070637</v>
       </c>
       <c r="C11">
-        <v>11496.57348596942</v>
+        <v>11412.77573591728</v>
       </c>
       <c r="D11">
-        <v>11979.02112486949</v>
+        <v>12029.92866802847</v>
       </c>
       <c r="E11">
-        <v>-2591.781682211795</v>
+        <v>-2457.076389000676</v>
       </c>
       <c r="F11">
-        <v>1212.347638900068</v>
+        <v>1347.052932111186</v>
       </c>
       <c r="G11">
         <v>729.9</v>
@@ -2195,28 +2195,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M11">
-        <v>60.98108623667339</v>
+        <v>67.75676248519267</v>
       </c>
       <c r="N11">
-        <v>769.3389137633267</v>
+        <v>762.5632375148074</v>
       </c>
       <c r="O11">
-        <v>191.8731250925737</v>
+        <v>190.183271436193</v>
       </c>
       <c r="P11">
-        <v>577.465788670753</v>
+        <v>572.3799660786144</v>
       </c>
       <c r="Q11">
-        <v>1154.565788670753</v>
+        <v>1149.479966078614</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1004104791513411</v>
+        <v>0.1008763883452293</v>
       </c>
       <c r="T11">
-        <v>1.261211989638363</v>
+        <v>1.271972017210838</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.61602508649074</v>
+        <v>12.25442257784166</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09456426751070637</v>
+        <v>0.09435703279369234</v>
       </c>
       <c r="C12">
-        <v>11412.77573591728</v>
+        <v>11329.4125186071</v>
       </c>
       <c r="D12">
-        <v>12029.92866802847</v>
+        <v>12081.27074392941</v>
       </c>
       <c r="E12">
-        <v>-2457.076389000676</v>
+        <v>-2322.371095789558</v>
       </c>
       <c r="F12">
-        <v>1347.052932111186</v>
+        <v>1481.758225322305</v>
       </c>
       <c r="G12">
         <v>729.9</v>
@@ -2277,28 +2277,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M12">
-        <v>67.75676248519267</v>
+        <v>74.53243873371194</v>
       </c>
       <c r="N12">
-        <v>762.5632375148074</v>
+        <v>755.7875612662881</v>
       </c>
       <c r="O12">
-        <v>190.183271436193</v>
+        <v>188.4934177798123</v>
       </c>
       <c r="P12">
-        <v>572.3799660786144</v>
+        <v>567.2941434864758</v>
       </c>
       <c r="Q12">
-        <v>1149.479966078614</v>
+        <v>1144.394143486476</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1008763883452293</v>
+        <v>0.1013527674086431</v>
       </c>
       <c r="T12">
-        <v>1.271972017210838</v>
+        <v>1.282973843155729</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.25442257784166</v>
+        <v>11.14038416167424</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09435703279369234</v>
+        <v>0.0941497980766783</v>
       </c>
       <c r="C13">
-        <v>11329.4125186071</v>
+        <v>11246.48942146261</v>
       </c>
       <c r="D13">
-        <v>12081.27074392941</v>
+        <v>12133.05293999603</v>
       </c>
       <c r="E13">
-        <v>-2322.371095789558</v>
+        <v>-2187.665802578439</v>
       </c>
       <c r="F13">
-        <v>1481.758225322305</v>
+        <v>1616.463518533423</v>
       </c>
       <c r="G13">
         <v>729.9</v>
@@ -2359,28 +2359,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M13">
-        <v>74.53243873371194</v>
+        <v>81.30811498223119</v>
       </c>
       <c r="N13">
-        <v>755.7875612662881</v>
+        <v>749.0118850177689</v>
       </c>
       <c r="O13">
-        <v>188.4934177798123</v>
+        <v>186.8035641234316</v>
       </c>
       <c r="P13">
-        <v>567.2941434864758</v>
+        <v>562.2083208943374</v>
       </c>
       <c r="Q13">
-        <v>1144.394143486476</v>
+        <v>1139.308320894337</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1013527674086431</v>
+        <v>0.1018399732689526</v>
       </c>
       <c r="T13">
-        <v>1.282973843155729</v>
+        <v>1.294225710599368</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.14038416167424</v>
+        <v>10.21201881486805</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0941497980766783</v>
+        <v>0.09394256335966426</v>
       </c>
       <c r="C14">
-        <v>11246.48942146261</v>
+        <v>11164.01212811414</v>
       </c>
       <c r="D14">
-        <v>12133.05293999603</v>
+        <v>12185.28093985869</v>
       </c>
       <c r="E14">
-        <v>-2187.665802578439</v>
+        <v>-2052.960509367321</v>
       </c>
       <c r="F14">
-        <v>1616.463518533423</v>
+        <v>1751.168811744542</v>
       </c>
       <c r="G14">
         <v>729.9</v>
@@ -2441,28 +2441,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M14">
-        <v>81.30811498223119</v>
+        <v>88.08379123075046</v>
       </c>
       <c r="N14">
-        <v>749.0118850177689</v>
+        <v>742.2362087692496</v>
       </c>
       <c r="O14">
-        <v>186.8035641234316</v>
+        <v>185.1137104670509</v>
       </c>
       <c r="P14">
-        <v>562.2083208943374</v>
+        <v>557.1224983021988</v>
       </c>
       <c r="Q14">
-        <v>1139.308320894337</v>
+        <v>1134.222498302199</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1018399732689526</v>
+        <v>0.1023383792639819</v>
       </c>
       <c r="T14">
-        <v>1.294225710599368</v>
+        <v>1.3057362416624</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.21201881486805</v>
+        <v>9.426478906032051</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09394256335966426</v>
+        <v>0.09389295464265025</v>
       </c>
       <c r="C15">
-        <v>11164.01212811414</v>
+        <v>11041.87616357857</v>
       </c>
       <c r="D15">
-        <v>12185.28093985869</v>
+        <v>12197.85026853423</v>
       </c>
       <c r="E15">
-        <v>-2052.960509367321</v>
+        <v>-1918.255216156202</v>
       </c>
       <c r="F15">
-        <v>1751.168811744542</v>
+        <v>1885.874104955661</v>
       </c>
       <c r="G15">
         <v>729.9</v>
@@ -2523,45 +2523,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M15">
-        <v>88.08379123075046</v>
+        <v>97.68827863670323</v>
       </c>
       <c r="N15">
-        <v>742.2362087692496</v>
+        <v>732.6317213632968</v>
       </c>
       <c r="O15">
-        <v>185.1137104670509</v>
+        <v>182.7183513080062</v>
       </c>
       <c r="P15">
-        <v>557.1224983021988</v>
+        <v>549.9133700552906</v>
       </c>
       <c r="Q15">
-        <v>1134.222498302199</v>
+        <v>1127.013370055291</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1023383792639819</v>
+        <v>0.1028483760961049</v>
       </c>
       <c r="T15">
-        <v>1.3057362416624</v>
+        <v>1.31751445949434</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.426478906032051</v>
+        <v>8.499689129418584</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09389295464265025</v>
+        <v>0.09369697892563621</v>
       </c>
       <c r="C16">
-        <v>11041.87616357857</v>
+        <v>10957.07970608165</v>
       </c>
       <c r="D16">
-        <v>12197.85026853423</v>
+        <v>12247.75910424843</v>
       </c>
       <c r="E16">
-        <v>-1918.255216156202</v>
+        <v>-1783.549922945083</v>
       </c>
       <c r="F16">
-        <v>1885.874104955661</v>
+        <v>2020.57939816678</v>
       </c>
       <c r="G16">
         <v>729.9</v>
@@ -2605,28 +2605,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M16">
-        <v>97.68827863670323</v>
+        <v>104.6660128250392</v>
       </c>
       <c r="N16">
-        <v>732.6317213632968</v>
+        <v>725.6539871749609</v>
       </c>
       <c r="O16">
-        <v>182.7183513080062</v>
+        <v>180.9781044014352</v>
       </c>
       <c r="P16">
-        <v>549.9133700552906</v>
+        <v>544.6758827735257</v>
       </c>
       <c r="Q16">
-        <v>1127.013370055291</v>
+        <v>1121.775882773526</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1028483760961049</v>
+        <v>0.1033703728536897</v>
       </c>
       <c r="T16">
-        <v>1.31751445949434</v>
+        <v>1.329569811863502</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.499689129418584</v>
+        <v>7.933043187457344</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09369697892563621</v>
+        <v>0.09350100320862217</v>
       </c>
       <c r="C17">
-        <v>10957.07970608165</v>
+        <v>10872.69334142163</v>
       </c>
       <c r="D17">
-        <v>12247.75910424843</v>
+        <v>12298.07803279953</v>
       </c>
       <c r="E17">
-        <v>-1783.549922945083</v>
+        <v>-1648.844629733965</v>
       </c>
       <c r="F17">
-        <v>2020.579398166779</v>
+        <v>2155.284691377898</v>
       </c>
       <c r="G17">
         <v>729.9</v>
@@ -2687,28 +2687,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M17">
-        <v>104.6660128250392</v>
+        <v>111.6437470133751</v>
       </c>
       <c r="N17">
-        <v>725.6539871749609</v>
+        <v>718.6762529866249</v>
       </c>
       <c r="O17">
-        <v>180.9781044014352</v>
+        <v>179.2378574948643</v>
       </c>
       <c r="P17">
-        <v>544.6758827735257</v>
+        <v>539.4383954917607</v>
       </c>
       <c r="Q17">
-        <v>1121.775882773526</v>
+        <v>1116.538395491761</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1033703728536897</v>
+        <v>0.1039047981055026</v>
       </c>
       <c r="T17">
-        <v>1.329569811863502</v>
+        <v>1.34191219643193</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.933043187457344</v>
+        <v>7.43722798824126</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09350100320862217</v>
+        <v>0.09330502749160814</v>
       </c>
       <c r="C18">
-        <v>10872.69334142163</v>
+        <v>10788.72214495002</v>
       </c>
       <c r="D18">
-        <v>12298.07803279953</v>
+        <v>12348.81212953904</v>
       </c>
       <c r="E18">
-        <v>-1648.844629733965</v>
+        <v>-1514.139336522846</v>
       </c>
       <c r="F18">
-        <v>2155.284691377898</v>
+        <v>2289.989984589017</v>
       </c>
       <c r="G18">
         <v>729.9</v>
@@ -2769,28 +2769,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M18">
-        <v>111.6437470133751</v>
+        <v>118.6214812017111</v>
       </c>
       <c r="N18">
-        <v>718.6762529866249</v>
+        <v>711.698518798289</v>
       </c>
       <c r="O18">
-        <v>179.2378574948643</v>
+        <v>177.4976105882933</v>
       </c>
       <c r="P18">
-        <v>539.4383954917607</v>
+        <v>534.2009082099958</v>
       </c>
       <c r="Q18">
-        <v>1116.538395491761</v>
+        <v>1111.300908209996</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1039047981055026</v>
+        <v>0.1044521010742267</v>
       </c>
       <c r="T18">
-        <v>1.34191219643193</v>
+        <v>1.354551987857429</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.43722798824126</v>
+        <v>6.999743988932951</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09330502749160814</v>
+        <v>0.09333873537459411</v>
       </c>
       <c r="C19">
-        <v>10788.72214495002</v>
+        <v>10645.26078553314</v>
       </c>
       <c r="D19">
-        <v>12348.81212953904</v>
+        <v>12340.05606333327</v>
       </c>
       <c r="E19">
-        <v>-1514.139336522846</v>
+        <v>-1379.434043311727</v>
       </c>
       <c r="F19">
-        <v>2289.989984589017</v>
+        <v>2424.695277800136</v>
       </c>
       <c r="G19">
         <v>729.9</v>
@@ -2851,45 +2851,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M19">
-        <v>118.6214812017111</v>
+        <v>129.7211973623072</v>
       </c>
       <c r="N19">
-        <v>711.698518798289</v>
+        <v>700.5988026376929</v>
       </c>
       <c r="O19">
-        <v>177.4976105882933</v>
+        <v>174.7293413778406</v>
       </c>
       <c r="P19">
-        <v>534.2009082099958</v>
+        <v>525.8694612598523</v>
       </c>
       <c r="Q19">
-        <v>1111.300908209996</v>
+        <v>1102.969461259852</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1044521010742267</v>
+        <v>0.1050127528958465</v>
       </c>
       <c r="T19">
-        <v>1.354551987857429</v>
+        <v>1.367500066878672</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.999743988932951</v>
+        <v>6.400804316359665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09333873537459413</v>
+        <v>0.09315551985758007</v>
       </c>
       <c r="C20">
-        <v>10645.26078553313</v>
+        <v>10558.2983902656</v>
       </c>
       <c r="D20">
-        <v>12340.05606333327</v>
+        <v>12387.79896127686</v>
       </c>
       <c r="E20">
-        <v>-1379.434043311728</v>
+        <v>-1244.728750100609</v>
       </c>
       <c r="F20">
-        <v>2424.695277800135</v>
+        <v>2559.400571011254</v>
       </c>
       <c r="G20">
         <v>729.9</v>
@@ -2933,28 +2933,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M20">
-        <v>129.7211973623072</v>
+        <v>136.9279305491021</v>
       </c>
       <c r="N20">
-        <v>700.5988026376929</v>
+        <v>693.3920694508979</v>
       </c>
       <c r="O20">
-        <v>174.7293413778406</v>
+        <v>172.9319821210539</v>
       </c>
       <c r="P20">
-        <v>525.8694612598523</v>
+        <v>520.460087329844</v>
       </c>
       <c r="Q20">
-        <v>1102.969461259852</v>
+        <v>1097.560087329844</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1050127528958465</v>
+        <v>0.1055872479723211</v>
       </c>
       <c r="T20">
-        <v>1.367500066878672</v>
+        <v>1.380767851554759</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.400804316359666</v>
+        <v>6.063919878656524</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09315551985758007</v>
+        <v>0.09297230434056607</v>
       </c>
       <c r="C21">
-        <v>10558.2983902656</v>
+        <v>10471.70685836176</v>
       </c>
       <c r="D21">
-        <v>12387.79896127686</v>
+        <v>12435.91272258413</v>
       </c>
       <c r="E21">
-        <v>-1244.728750100609</v>
+        <v>-1110.02345688949</v>
       </c>
       <c r="F21">
-        <v>2559.400571011254</v>
+        <v>2694.105864222372</v>
       </c>
       <c r="G21">
         <v>729.9</v>
@@ -3015,28 +3015,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M21">
-        <v>136.9279305491021</v>
+        <v>144.1346637358969</v>
       </c>
       <c r="N21">
-        <v>693.3920694508979</v>
+        <v>686.1853362641032</v>
       </c>
       <c r="O21">
-        <v>172.9319821210539</v>
+        <v>171.1346228642673</v>
       </c>
       <c r="P21">
-        <v>520.460087329844</v>
+        <v>515.0507133998358</v>
       </c>
       <c r="Q21">
-        <v>1097.560087329844</v>
+        <v>1092.150713399836</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1055872479723211</v>
+        <v>0.1061761054257076</v>
       </c>
       <c r="T21">
-        <v>1.380767851554759</v>
+        <v>1.39436733084775</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.063919878656524</v>
+        <v>5.760723884723698</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09297230434056607</v>
+        <v>0.09291518962355202</v>
       </c>
       <c r="C22">
-        <v>10471.70685836176</v>
+        <v>10352.07682307991</v>
       </c>
       <c r="D22">
-        <v>12435.91272258413</v>
+        <v>12450.9879805134</v>
       </c>
       <c r="E22">
-        <v>-1110.02345688949</v>
+        <v>-975.3181636783715</v>
       </c>
       <c r="F22">
-        <v>2694.105864222372</v>
+        <v>2828.811157433491</v>
       </c>
       <c r="G22">
         <v>729.9</v>
@@ -3097,45 +3097,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M22">
-        <v>144.1346637358969</v>
+        <v>153.6044458486386</v>
       </c>
       <c r="N22">
-        <v>686.1853362641032</v>
+        <v>676.7155541513615</v>
       </c>
       <c r="O22">
-        <v>171.1346228642673</v>
+        <v>168.7728592053496</v>
       </c>
       <c r="P22">
-        <v>515.0507133998358</v>
+        <v>507.942694946012</v>
       </c>
       <c r="Q22">
-        <v>1092.150713399836</v>
+        <v>1085.042694946012</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1061761054257076</v>
+        <v>0.1067798706627241</v>
       </c>
       <c r="T22">
-        <v>1.39436733084775</v>
+        <v>1.408311100755752</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.760723884723698</v>
+        <v>5.405572706002243</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09291518962355202</v>
+        <v>0.09273797890653798</v>
       </c>
       <c r="C23">
-        <v>10352.07682307991</v>
+        <v>10264.37927410835</v>
       </c>
       <c r="D23">
-        <v>12450.9879805134</v>
+        <v>12497.99572475295</v>
       </c>
       <c r="E23">
-        <v>-975.3181636783715</v>
+        <v>-840.6128704672528</v>
       </c>
       <c r="F23">
-        <v>2828.811157433491</v>
+        <v>2963.51645064461</v>
       </c>
       <c r="G23">
         <v>729.9</v>
@@ -3179,28 +3179,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M23">
-        <v>153.6044458486386</v>
+        <v>160.9189432700023</v>
       </c>
       <c r="N23">
-        <v>676.7155541513615</v>
+        <v>669.4010567299977</v>
       </c>
       <c r="O23">
-        <v>168.7728592053496</v>
+        <v>166.9486235484614</v>
       </c>
       <c r="P23">
-        <v>507.942694946012</v>
+        <v>502.4524331815362</v>
       </c>
       <c r="Q23">
-        <v>1085.042694946012</v>
+        <v>1079.552433181536</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1067798706627241</v>
+        <v>0.1073991170596641</v>
       </c>
       <c r="T23">
-        <v>1.408311100755752</v>
+        <v>1.422612403225499</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.405572706002243</v>
+        <v>5.159864855729412</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09273797890653798</v>
+        <v>0.09256076818952395</v>
       </c>
       <c r="C24">
-        <v>10264.37927410835</v>
+        <v>10177.03801851622</v>
       </c>
       <c r="D24">
-        <v>12497.99572475295</v>
+        <v>12545.35976237195</v>
       </c>
       <c r="E24">
-        <v>-840.6128704672528</v>
+        <v>-705.9075772561341</v>
       </c>
       <c r="F24">
-        <v>2963.51645064461</v>
+        <v>3098.221743855729</v>
       </c>
       <c r="G24">
         <v>729.9</v>
@@ -3261,28 +3261,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M24">
-        <v>160.9189432700023</v>
+        <v>168.2334406913661</v>
       </c>
       <c r="N24">
-        <v>669.4010567299977</v>
+        <v>662.0865593086339</v>
       </c>
       <c r="O24">
-        <v>166.9486235484614</v>
+        <v>165.1243878915733</v>
       </c>
       <c r="P24">
-        <v>502.4524331815362</v>
+        <v>496.9621714170606</v>
       </c>
       <c r="Q24">
-        <v>1079.552433181536</v>
+        <v>1074.062171417061</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1073991170596641</v>
+        <v>0.1080344477786025</v>
       </c>
       <c r="T24">
-        <v>1.422612403225499</v>
+        <v>1.437285168097056</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.159864855729412</v>
+        <v>4.935522905480306</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09256076818952395</v>
+        <v>0.09238355747250993</v>
       </c>
       <c r="C25">
-        <v>10177.03801851622</v>
+        <v>10090.0571224811</v>
       </c>
       <c r="D25">
-        <v>12545.35976237195</v>
+        <v>12593.08415954795</v>
       </c>
       <c r="E25">
-        <v>-705.9075772561341</v>
+        <v>-571.2022840450154</v>
       </c>
       <c r="F25">
-        <v>3098.221743855729</v>
+        <v>3232.927037066847</v>
       </c>
       <c r="G25">
         <v>729.9</v>
@@ -3343,28 +3343,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M25">
-        <v>168.2334406913661</v>
+        <v>175.5479381127298</v>
       </c>
       <c r="N25">
-        <v>662.0865593086339</v>
+        <v>654.7720618872702</v>
       </c>
       <c r="O25">
-        <v>165.1243878915733</v>
+        <v>163.3001522346852</v>
       </c>
       <c r="P25">
-        <v>496.9621714170606</v>
+        <v>491.471909652585</v>
       </c>
       <c r="Q25">
-        <v>1074.062171417061</v>
+        <v>1068.571909652585</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1080344477786025</v>
+        <v>0.1086864977269867</v>
       </c>
       <c r="T25">
-        <v>1.437285168097056</v>
+        <v>1.452344058359971</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.935522905480306</v>
+        <v>4.729876117751961</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09238355747250993</v>
+        <v>0.0922063467554959</v>
       </c>
       <c r="C26">
-        <v>10090.0571224811</v>
+        <v>10003.44071429016</v>
       </c>
       <c r="D26">
-        <v>12593.08415954795</v>
+        <v>12641.17304456812</v>
       </c>
       <c r="E26">
-        <v>-571.2022840450159</v>
+        <v>-436.4969908338971</v>
       </c>
       <c r="F26">
-        <v>3232.927037066847</v>
+        <v>3367.632330277966</v>
       </c>
       <c r="G26">
         <v>729.9</v>
@@ -3425,28 +3425,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M26">
-        <v>175.5479381127298</v>
+        <v>182.8624355340935</v>
       </c>
       <c r="N26">
-        <v>654.7720618872703</v>
+        <v>647.4575644659066</v>
       </c>
       <c r="O26">
-        <v>163.3001522346852</v>
+        <v>161.4759165777971</v>
       </c>
       <c r="P26">
-        <v>491.4719096525851</v>
+        <v>485.9816478881095</v>
       </c>
       <c r="Q26">
-        <v>1068.571909652585</v>
+        <v>1063.08164788811</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1086864977269867</v>
+        <v>0.1093559356739945</v>
       </c>
       <c r="T26">
-        <v>1.452344058359971</v>
+        <v>1.467804519029897</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.729876117751962</v>
+        <v>4.540681073041884</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0922063467554959</v>
+        <v>0.09202913603848185</v>
       </c>
       <c r="C27">
-        <v>10003.44071429016</v>
+        <v>9917.192985530637</v>
       </c>
       <c r="D27">
-        <v>12641.17304456812</v>
+        <v>12689.63060901972</v>
       </c>
       <c r="E27">
-        <v>-436.4969908338971</v>
+        <v>-301.7916976227784</v>
       </c>
       <c r="F27">
-        <v>3367.632330277966</v>
+        <v>3502.337623489084</v>
       </c>
       <c r="G27">
         <v>729.9</v>
@@ -3507,28 +3507,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M27">
-        <v>182.8624355340935</v>
+        <v>190.1769329554573</v>
       </c>
       <c r="N27">
-        <v>647.4575644659066</v>
+        <v>640.1430670445427</v>
       </c>
       <c r="O27">
-        <v>161.4759165777971</v>
+        <v>159.6516809209089</v>
       </c>
       <c r="P27">
-        <v>485.9816478881095</v>
+        <v>480.4913861236338</v>
       </c>
       <c r="Q27">
-        <v>1063.08164788811</v>
+        <v>1057.591386123634</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1093559356739945</v>
+        <v>0.110043466538489</v>
       </c>
       <c r="T27">
-        <v>1.467804519029897</v>
+        <v>1.483682829988199</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.540681073041884</v>
+        <v>4.366039493309502</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09202913603848185</v>
+        <v>0.09205458732146783</v>
       </c>
       <c r="C28">
-        <v>9917.192985530637</v>
+        <v>9775.505306391544</v>
       </c>
       <c r="D28">
-        <v>12689.63060901972</v>
+        <v>12682.64822309175</v>
       </c>
       <c r="E28">
-        <v>-301.7916976227784</v>
+        <v>-167.0864044116597</v>
       </c>
       <c r="F28">
-        <v>3502.337623489084</v>
+        <v>3637.042916700203</v>
       </c>
       <c r="G28">
         <v>729.9</v>
@@ -3589,45 +3589,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M28">
-        <v>190.1769329554573</v>
+        <v>201.1284732935212</v>
       </c>
       <c r="N28">
-        <v>640.1430670445427</v>
+        <v>629.1915267064788</v>
       </c>
       <c r="O28">
-        <v>159.6516809209089</v>
+        <v>156.9203667605958</v>
       </c>
       <c r="P28">
-        <v>480.4913861236338</v>
+        <v>472.271159945883</v>
       </c>
       <c r="Q28">
-        <v>1057.591386123634</v>
+        <v>1049.371159945883</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.110043466538489</v>
+        <v>0.1107498338650244</v>
       </c>
       <c r="T28">
-        <v>1.483682829988199</v>
+        <v>1.499996163164536</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.366039493309502</v>
+        <v>4.12830658137724</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09205458732146783</v>
+        <v>0.09188488260445381</v>
       </c>
       <c r="C29">
-        <v>9775.505306391544</v>
+        <v>9687.503077310184</v>
       </c>
       <c r="D29">
-        <v>12682.64822309175</v>
+        <v>12729.35128722151</v>
       </c>
       <c r="E29">
-        <v>-167.0864044116597</v>
+        <v>-32.381111200541</v>
       </c>
       <c r="F29">
-        <v>3637.042916700203</v>
+        <v>3771.748209911322</v>
       </c>
       <c r="G29">
         <v>729.9</v>
@@ -3671,28 +3671,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M29">
-        <v>201.1284732935212</v>
+        <v>208.5776760080961</v>
       </c>
       <c r="N29">
-        <v>629.1915267064788</v>
+        <v>621.742323991904</v>
       </c>
       <c r="O29">
-        <v>156.9203667605958</v>
+        <v>155.0625356035808</v>
       </c>
       <c r="P29">
-        <v>472.271159945883</v>
+        <v>466.6797883883231</v>
       </c>
       <c r="Q29">
-        <v>1049.371159945883</v>
+        <v>1043.779788388323</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1107498338650244</v>
+        <v>0.1114758225061858</v>
       </c>
       <c r="T29">
-        <v>1.499996163164536</v>
+        <v>1.516762644484661</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.12830658137724</v>
+        <v>3.980867060613767</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09188488260445381</v>
+        <v>0.09171517788743977</v>
       </c>
       <c r="C30">
-        <v>9687.503077310184</v>
+        <v>9599.846081794132</v>
       </c>
       <c r="D30">
-        <v>12729.35128722151</v>
+        <v>12776.39958491657</v>
       </c>
       <c r="E30">
-        <v>-32.381111200541</v>
+        <v>102.3241820105777</v>
       </c>
       <c r="F30">
-        <v>3771.748209911322</v>
+        <v>3906.45350312244</v>
       </c>
       <c r="G30">
         <v>729.9</v>
@@ -3753,28 +3753,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M30">
-        <v>208.5776760080961</v>
+        <v>216.026878722671</v>
       </c>
       <c r="N30">
-        <v>621.742323991904</v>
+        <v>614.2931212773291</v>
       </c>
       <c r="O30">
-        <v>155.0625356035808</v>
+        <v>153.2047044465659</v>
       </c>
       <c r="P30">
-        <v>466.6797883883231</v>
+        <v>461.0884168307632</v>
       </c>
       <c r="Q30">
-        <v>1043.779788388323</v>
+        <v>1038.188416830763</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1114758225061858</v>
+        <v>0.1122222615316053</v>
       </c>
       <c r="T30">
-        <v>1.516762644484661</v>
+        <v>1.53400142105324</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.980867060613767</v>
+        <v>3.843595782661568</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09171517788743976</v>
+        <v>0.09154547317042572</v>
       </c>
       <c r="C31">
-        <v>9599.846081794136</v>
+        <v>9512.538162044186</v>
       </c>
       <c r="D31">
-        <v>12776.39958491658</v>
+        <v>12823.79695837774</v>
       </c>
       <c r="E31">
-        <v>102.3241820105773</v>
+        <v>237.029475221696</v>
       </c>
       <c r="F31">
-        <v>3906.45350312244</v>
+        <v>4041.158796333559</v>
       </c>
       <c r="G31">
         <v>729.9</v>
@@ -3835,28 +3835,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M31">
-        <v>216.0268787226709</v>
+        <v>223.4760814372458</v>
       </c>
       <c r="N31">
-        <v>614.2931212773291</v>
+        <v>606.8439185627542</v>
       </c>
       <c r="O31">
-        <v>153.2047044465659</v>
+        <v>151.3468732895509</v>
       </c>
       <c r="P31">
-        <v>461.0884168307632</v>
+        <v>455.4970452732033</v>
       </c>
       <c r="Q31">
-        <v>1038.188416830763</v>
+        <v>1032.597045273203</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1122222615316053</v>
+        <v>0.1129900273863225</v>
       </c>
       <c r="T31">
-        <v>1.53400142105324</v>
+        <v>1.551732734095207</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.843595782661568</v>
+        <v>3.715475923239516</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09154547317042572</v>
+        <v>0.09137576845341169</v>
       </c>
       <c r="C32">
-        <v>9512.538162044186</v>
+        <v>9425.583217488</v>
       </c>
       <c r="D32">
-        <v>12823.79695837774</v>
+        <v>12871.54730703268</v>
       </c>
       <c r="E32">
-        <v>237.029475221696</v>
+        <v>371.7347684328142</v>
       </c>
       <c r="F32">
-        <v>4041.158796333559</v>
+        <v>4175.864089544677</v>
       </c>
       <c r="G32">
         <v>729.9</v>
@@ -3917,28 +3917,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M32">
-        <v>223.4760814372458</v>
+        <v>230.9252841518206</v>
       </c>
       <c r="N32">
-        <v>606.8439185627542</v>
+        <v>599.3947158481794</v>
       </c>
       <c r="O32">
-        <v>151.3468732895509</v>
+        <v>149.489042132536</v>
       </c>
       <c r="P32">
-        <v>455.4970452732033</v>
+        <v>449.9056737156435</v>
       </c>
       <c r="Q32">
-        <v>1032.597045273203</v>
+        <v>1027.005673715644</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1129900273863225</v>
+        <v>0.1137800473237851</v>
       </c>
       <c r="T32">
-        <v>1.551732734095207</v>
+        <v>1.56997799823984</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.715475923239516</v>
+        <v>3.595621861199532</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09137576845341169</v>
+        <v>0.09120606373639767</v>
       </c>
       <c r="C33">
-        <v>9425.583217488</v>
+        <v>9338.985205849531</v>
       </c>
       <c r="D33">
-        <v>12871.54730703268</v>
+        <v>12919.65458860533</v>
       </c>
       <c r="E33">
-        <v>371.7347684328142</v>
+        <v>506.4400616439334</v>
       </c>
       <c r="F33">
-        <v>4175.864089544677</v>
+        <v>4310.569382755796</v>
       </c>
       <c r="G33">
         <v>729.9</v>
@@ -3999,28 +3999,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M33">
-        <v>230.9252841518206</v>
+        <v>238.3744868663955</v>
       </c>
       <c r="N33">
-        <v>599.3947158481794</v>
+        <v>591.9455131336045</v>
       </c>
       <c r="O33">
-        <v>149.489042132536</v>
+        <v>147.631210975521</v>
       </c>
       <c r="P33">
-        <v>449.9056737156435</v>
+        <v>444.3143021580836</v>
       </c>
       <c r="Q33">
-        <v>1027.005673715644</v>
+        <v>1021.414302158084</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1137800473237851</v>
+        <v>0.1145933031417613</v>
       </c>
       <c r="T33">
-        <v>1.56997799823984</v>
+        <v>1.588759887800492</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.595621861199532</v>
+        <v>3.483258678037046</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09120606373639767</v>
+        <v>0.09103635901938364</v>
       </c>
       <c r="C34">
-        <v>9338.985205849531</v>
+        <v>9252.748144242523</v>
       </c>
       <c r="D34">
-        <v>12919.65458860533</v>
+        <v>12968.12282020944</v>
       </c>
       <c r="E34">
-        <v>506.4400616439334</v>
+        <v>641.1453548550517</v>
       </c>
       <c r="F34">
-        <v>4310.569382755796</v>
+        <v>4445.274675966914</v>
       </c>
       <c r="G34">
         <v>729.9</v>
@@ -4081,28 +4081,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M34">
-        <v>238.3744868663955</v>
+        <v>245.8236895809704</v>
       </c>
       <c r="N34">
-        <v>591.9455131336045</v>
+        <v>584.4963104190297</v>
       </c>
       <c r="O34">
-        <v>147.631210975521</v>
+        <v>145.773379818506</v>
       </c>
       <c r="P34">
-        <v>444.3143021580836</v>
+        <v>438.7229306005237</v>
       </c>
       <c r="Q34">
-        <v>1021.414302158084</v>
+        <v>1015.822930600524</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1145933031417613</v>
+        <v>0.1154308352528114</v>
       </c>
       <c r="T34">
-        <v>1.588759887800492</v>
+        <v>1.608102430780864</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.483258678037046</v>
+        <v>3.377705384763196</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09103635901938364</v>
+        <v>0.09086665430236962</v>
       </c>
       <c r="C35">
-        <v>9252.748144242523</v>
+        <v>9166.876110288702</v>
       </c>
       <c r="D35">
-        <v>12968.12282020944</v>
+        <v>13016.95607946674</v>
       </c>
       <c r="E35">
-        <v>641.1453548550517</v>
+        <v>775.8506480661708</v>
       </c>
       <c r="F35">
-        <v>4445.274675966914</v>
+        <v>4579.979969178034</v>
       </c>
       <c r="G35">
         <v>729.9</v>
@@ -4163,28 +4163,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M35">
-        <v>245.8236895809704</v>
+        <v>253.2728922955453</v>
       </c>
       <c r="N35">
-        <v>584.4963104190297</v>
+        <v>577.0471077044548</v>
       </c>
       <c r="O35">
-        <v>145.773379818506</v>
+        <v>143.915548661491</v>
       </c>
       <c r="P35">
-        <v>438.7229306005237</v>
+        <v>433.1315590429638</v>
       </c>
       <c r="Q35">
-        <v>1015.822930600524</v>
+        <v>1010.231559042964</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1154308352528114</v>
+        <v>0.1162937471248024</v>
       </c>
       <c r="T35">
-        <v>1.608102430780864</v>
+        <v>1.628031111427308</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.377705384763196</v>
+        <v>3.278361108740749</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09086665430236962</v>
+        <v>0.09069694958535557</v>
       </c>
       <c r="C36">
-        <v>9166.876110288702</v>
+        <v>9081.373243261365</v>
       </c>
       <c r="D36">
-        <v>13016.95607946674</v>
+        <v>13066.15850565052</v>
       </c>
       <c r="E36">
-        <v>775.8506480661708</v>
+        <v>910.5559412772891</v>
       </c>
       <c r="F36">
-        <v>4579.979969178034</v>
+        <v>4714.685262389152</v>
       </c>
       <c r="G36">
         <v>729.9</v>
@@ -4245,28 +4245,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M36">
-        <v>253.2728922955453</v>
+        <v>260.7220950101201</v>
       </c>
       <c r="N36">
-        <v>577.0471077044548</v>
+        <v>569.5979049898799</v>
       </c>
       <c r="O36">
-        <v>143.915548661491</v>
+        <v>142.057717504476</v>
       </c>
       <c r="P36">
-        <v>433.1315590429638</v>
+        <v>427.5401874854039</v>
       </c>
       <c r="Q36">
-        <v>1010.231559042964</v>
+        <v>1004.640187485404</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1162937471248024</v>
+        <v>0.1171832101313163</v>
       </c>
       <c r="T36">
-        <v>1.628031111427308</v>
+        <v>1.648572982247489</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.278361108740749</v>
+        <v>3.184693648491014</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09069694958535557</v>
+        <v>0.09052724486834153</v>
       </c>
       <c r="C37">
-        <v>9081.373243261365</v>
+        <v>8996.243745254913</v>
       </c>
       <c r="D37">
-        <v>13066.15850565052</v>
+        <v>13115.73430085518</v>
       </c>
       <c r="E37">
-        <v>910.5559412772891</v>
+        <v>1045.261234488408</v>
       </c>
       <c r="F37">
-        <v>4714.685262389152</v>
+        <v>4849.390555600271</v>
       </c>
       <c r="G37">
         <v>729.9</v>
@@ -4327,28 +4327,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M37">
-        <v>260.7220950101201</v>
+        <v>268.171297724695</v>
       </c>
       <c r="N37">
-        <v>569.5979049898799</v>
+        <v>562.148702275305</v>
       </c>
       <c r="O37">
-        <v>142.057717504476</v>
+        <v>140.1998863474611</v>
       </c>
       <c r="P37">
-        <v>427.5401874854039</v>
+        <v>421.948815927844</v>
       </c>
       <c r="Q37">
-        <v>1004.640187485404</v>
+        <v>999.048815927844</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1171832101313163</v>
+        <v>0.1181004688567837</v>
       </c>
       <c r="T37">
-        <v>1.648572982247489</v>
+        <v>1.669756786530801</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.184693648491014</v>
+        <v>3.096229936032929</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09052724486834154</v>
+        <v>0.09035754015132752</v>
       </c>
       <c r="C38">
-        <v>8996.243745254911</v>
+        <v>8911.491882381248</v>
       </c>
       <c r="D38">
-        <v>13115.73430085518</v>
+        <v>13165.68773119264</v>
       </c>
       <c r="E38">
-        <v>1045.261234488407</v>
+        <v>1179.966527699527</v>
       </c>
       <c r="F38">
-        <v>4849.39055560027</v>
+        <v>4984.095848811389</v>
       </c>
       <c r="G38">
         <v>729.9</v>
@@ -4409,28 +4409,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M38">
-        <v>268.171297724695</v>
+        <v>275.6205004392698</v>
       </c>
       <c r="N38">
-        <v>562.1487022753051</v>
+        <v>554.6994995607301</v>
       </c>
       <c r="O38">
-        <v>140.1998863474611</v>
+        <v>138.3420551904461</v>
       </c>
       <c r="P38">
-        <v>421.9488159278441</v>
+        <v>416.357444370284</v>
       </c>
       <c r="Q38">
-        <v>999.0488159278441</v>
+        <v>993.4574443702841</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1181004688567837</v>
+        <v>0.1190468469068691</v>
       </c>
       <c r="T38">
-        <v>1.669756786530801</v>
+        <v>1.691613092537392</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.09622993603293</v>
+        <v>3.012548045869877</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09035754015132752</v>
+        <v>0.09090090543431348</v>
       </c>
       <c r="C39">
-        <v>8911.491882381248</v>
+        <v>8618.169426812197</v>
       </c>
       <c r="D39">
-        <v>13165.68773119264</v>
+        <v>13007.07056883471</v>
       </c>
       <c r="E39">
-        <v>1179.966527699527</v>
+        <v>1314.671820910645</v>
       </c>
       <c r="F39">
-        <v>4984.095848811389</v>
+        <v>5118.801142022508</v>
       </c>
       <c r="G39">
         <v>729.9</v>
@@ -4491,45 +4491,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M39">
-        <v>275.6205004392698</v>
+        <v>295.866706008901</v>
       </c>
       <c r="N39">
-        <v>554.6994995607301</v>
+        <v>534.4532939910991</v>
       </c>
       <c r="O39">
-        <v>138.3420551904461</v>
+        <v>133.2926515213801</v>
       </c>
       <c r="P39">
-        <v>416.357444370284</v>
+        <v>401.1606424697191</v>
       </c>
       <c r="Q39">
-        <v>993.4574443702841</v>
+        <v>978.2606424697191</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1190468469068691</v>
+        <v>0.1200237532811508</v>
       </c>
       <c r="T39">
-        <v>1.691613092537392</v>
+        <v>1.714174440673228</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.012548045869877</v>
+        <v>2.80639890577962</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09090090543431348</v>
+        <v>0.09074996571729946</v>
       </c>
       <c r="C40">
-        <v>8618.169426812197</v>
+        <v>8527.141220324322</v>
       </c>
       <c r="D40">
-        <v>13007.07056883471</v>
+        <v>13050.74765555795</v>
       </c>
       <c r="E40">
-        <v>1314.671820910645</v>
+        <v>1449.377114121764</v>
       </c>
       <c r="F40">
-        <v>5118.801142022508</v>
+        <v>5253.506435233627</v>
       </c>
       <c r="G40">
         <v>729.9</v>
@@ -4573,28 +4573,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M40">
-        <v>295.866706008901</v>
+        <v>303.6526719565036</v>
       </c>
       <c r="N40">
-        <v>534.4532939910991</v>
+        <v>526.6673280434964</v>
       </c>
       <c r="O40">
-        <v>133.2926515213801</v>
+        <v>131.350831614048</v>
       </c>
       <c r="P40">
-        <v>401.1606424697191</v>
+        <v>395.3164964294484</v>
       </c>
       <c r="Q40">
-        <v>978.2606424697191</v>
+        <v>972.4164964294484</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1200237532811508</v>
+        <v>0.121032689372622</v>
       </c>
       <c r="T40">
-        <v>1.714174440673228</v>
+        <v>1.737475505141387</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.80639890577962</v>
+        <v>2.734439959477577</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09074996571729946</v>
+        <v>0.09059902600028542</v>
       </c>
       <c r="C41">
-        <v>8527.141220324322</v>
+        <v>8436.407333052673</v>
       </c>
       <c r="D41">
-        <v>13050.74765555795</v>
+        <v>13094.71906149742</v>
       </c>
       <c r="E41">
-        <v>1449.377114121764</v>
+        <v>1584.082407332882</v>
       </c>
       <c r="F41">
-        <v>5253.506435233627</v>
+        <v>5388.211728444745</v>
       </c>
       <c r="G41">
         <v>729.9</v>
@@ -4655,28 +4655,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M41">
-        <v>303.6526719565036</v>
+        <v>311.4386379041063</v>
       </c>
       <c r="N41">
-        <v>526.6673280434964</v>
+        <v>518.8813620958938</v>
       </c>
       <c r="O41">
-        <v>131.350831614048</v>
+        <v>129.4090117067159</v>
       </c>
       <c r="P41">
-        <v>395.3164964294484</v>
+        <v>389.4723503891779</v>
       </c>
       <c r="Q41">
-        <v>972.4164964294484</v>
+        <v>966.5723503891779</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.121032689372622</v>
+        <v>0.1220752566671424</v>
       </c>
       <c r="T41">
-        <v>1.737475505141387</v>
+        <v>1.761553271758484</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.734439959477577</v>
+        <v>2.666078960490639</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09059902600028542</v>
+        <v>0.09044808628327139</v>
       </c>
       <c r="C42">
-        <v>8436.407333052673</v>
+        <v>8345.970749971271</v>
       </c>
       <c r="D42">
-        <v>13094.71906149742</v>
+        <v>13138.98777162714</v>
       </c>
       <c r="E42">
-        <v>1584.082407332882</v>
+        <v>1718.787700544001</v>
       </c>
       <c r="F42">
-        <v>5388.211728444745</v>
+        <v>5522.917021655864</v>
       </c>
       <c r="G42">
         <v>729.9</v>
@@ -4737,28 +4737,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M42">
-        <v>311.4386379041063</v>
+        <v>319.224603851709</v>
       </c>
       <c r="N42">
-        <v>518.8813620958938</v>
+        <v>511.0953961482911</v>
       </c>
       <c r="O42">
-        <v>129.4090117067159</v>
+        <v>127.4671917993838</v>
       </c>
       <c r="P42">
-        <v>389.4723503891779</v>
+        <v>383.6282043489073</v>
       </c>
       <c r="Q42">
-        <v>966.5723503891779</v>
+        <v>960.7282043489073</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1220752566671424</v>
+        <v>0.1231531652258837</v>
       </c>
       <c r="T42">
-        <v>1.761553271758484</v>
+        <v>1.786447233854127</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.666078960490639</v>
+        <v>2.60105264438111</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09044808628327139</v>
+        <v>0.09029714656625736</v>
       </c>
       <c r="C43">
-        <v>8345.970749971271</v>
+        <v>8255.834496555708</v>
       </c>
       <c r="D43">
-        <v>13138.98777162714</v>
+        <v>13183.55681142269</v>
       </c>
       <c r="E43">
-        <v>1718.787700544001</v>
+        <v>1853.49299375512</v>
       </c>
       <c r="F43">
-        <v>5522.917021655864</v>
+        <v>5657.622314866982</v>
       </c>
       <c r="G43">
         <v>729.9</v>
@@ -4819,28 +4819,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M43">
-        <v>319.224603851709</v>
+        <v>327.0105697993116</v>
       </c>
       <c r="N43">
-        <v>511.0953961482911</v>
+        <v>503.3094302006884</v>
       </c>
       <c r="O43">
-        <v>127.4671917993838</v>
+        <v>125.5253718920517</v>
       </c>
       <c r="P43">
-        <v>383.6282043489073</v>
+        <v>377.7840583086368</v>
       </c>
       <c r="Q43">
-        <v>960.7282043489073</v>
+        <v>954.8840583086368</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1231531652258837</v>
+        <v>0.1242682430452713</v>
       </c>
       <c r="T43">
-        <v>1.786447233854127</v>
+        <v>1.812199608435827</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.60105264438111</v>
+        <v>2.539122819514894</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09029714656625736</v>
+        <v>0.09127585984924332</v>
       </c>
       <c r="C44">
-        <v>8255.834496555708</v>
+        <v>7837.397961953801</v>
       </c>
       <c r="D44">
-        <v>13183.55681142269</v>
+        <v>12899.8255700319</v>
       </c>
       <c r="E44">
-        <v>1853.49299375512</v>
+        <v>1988.198286966238</v>
       </c>
       <c r="F44">
-        <v>5657.622314866982</v>
+        <v>5792.327608078101</v>
       </c>
       <c r="G44">
         <v>729.9</v>
@@ -4901,45 +4901,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M44">
-        <v>327.0105697993116</v>
+        <v>355.0696823751876</v>
       </c>
       <c r="N44">
-        <v>503.3094302006884</v>
+        <v>475.2503176248125</v>
       </c>
       <c r="O44">
-        <v>125.5253718920517</v>
+        <v>118.5274292156282</v>
       </c>
       <c r="P44">
-        <v>377.7840583086368</v>
+        <v>356.7228884091842</v>
       </c>
       <c r="Q44">
-        <v>954.8840583086368</v>
+        <v>933.8228884091843</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1242682430452713</v>
+        <v>0.1254224464021813</v>
       </c>
       <c r="T44">
-        <v>1.812199608435827</v>
+        <v>1.838855575108112</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.539122819514894</v>
+        <v>2.338470562864432</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09127585984924332</v>
+        <v>0.0911511911322293</v>
       </c>
       <c r="C45">
-        <v>7837.397961953801</v>
+        <v>7738.153803574432</v>
       </c>
       <c r="D45">
-        <v>12899.8255700319</v>
+        <v>12935.28670486365</v>
       </c>
       <c r="E45">
-        <v>1988.198286966238</v>
+        <v>2122.903580177357</v>
       </c>
       <c r="F45">
-        <v>5792.327608078101</v>
+        <v>5927.03290128922</v>
       </c>
       <c r="G45">
         <v>729.9</v>
@@ -4983,28 +4983,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M45">
-        <v>355.0696823751876</v>
+        <v>363.3271168490292</v>
       </c>
       <c r="N45">
-        <v>475.2503176248125</v>
+        <v>466.9928831509709</v>
       </c>
       <c r="O45">
-        <v>118.5274292156282</v>
+        <v>116.4680250578521</v>
       </c>
       <c r="P45">
-        <v>356.7228884091842</v>
+        <v>350.5248580931187</v>
       </c>
       <c r="Q45">
-        <v>933.8228884091843</v>
+        <v>927.6248580931187</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1254224464021813</v>
+        <v>0.1266178713075523</v>
       </c>
       <c r="T45">
-        <v>1.838855575108112</v>
+        <v>1.866463540590122</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.338470562864432</v>
+        <v>2.285323504617513</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0911511911322293</v>
+        <v>0.09197227841521527</v>
       </c>
       <c r="C46">
-        <v>7738.153803574432</v>
+        <v>7373.418722367383</v>
       </c>
       <c r="D46">
-        <v>12935.28670486365</v>
+        <v>12705.25691686772</v>
       </c>
       <c r="E46">
-        <v>2122.903580177357</v>
+        <v>2257.608873388475</v>
       </c>
       <c r="F46">
-        <v>5927.03290128922</v>
+        <v>6061.738194500338</v>
       </c>
       <c r="G46">
         <v>729.9</v>
@@ -5065,45 +5065,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M46">
-        <v>363.3271168490292</v>
+        <v>388.5574182674717</v>
       </c>
       <c r="N46">
-        <v>466.9928831509709</v>
+        <v>441.7625817325284</v>
       </c>
       <c r="O46">
-        <v>116.4680250578521</v>
+        <v>110.1755878840926</v>
       </c>
       <c r="P46">
-        <v>350.5248580931187</v>
+        <v>331.5869938484358</v>
       </c>
       <c r="Q46">
-        <v>927.6248580931187</v>
+        <v>908.6869938484358</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1266178713075523</v>
+        <v>0.1278567662094823</v>
       </c>
       <c r="T46">
-        <v>1.866463540590122</v>
+        <v>1.89507543208966</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.285323504617513</v>
+        <v>2.136929990173117</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09197227841521527</v>
+        <v>0.09186862649820124</v>
       </c>
       <c r="C47">
-        <v>7373.418722367383</v>
+        <v>7267.299569783673</v>
       </c>
       <c r="D47">
-        <v>12705.25691686772</v>
+        <v>12733.84305749513</v>
       </c>
       <c r="E47">
-        <v>2257.608873388475</v>
+        <v>2392.314166599595</v>
       </c>
       <c r="F47">
-        <v>6061.738194500338</v>
+        <v>6196.443487711457</v>
       </c>
       <c r="G47">
         <v>729.9</v>
@@ -5147,28 +5147,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M47">
-        <v>388.5574182674717</v>
+        <v>397.1920275623044</v>
       </c>
       <c r="N47">
-        <v>441.7625817325284</v>
+        <v>433.1279724376956</v>
       </c>
       <c r="O47">
-        <v>110.1755878840926</v>
+        <v>108.0221163259613</v>
       </c>
       <c r="P47">
-        <v>331.5869938484358</v>
+        <v>325.1058561117343</v>
       </c>
       <c r="Q47">
-        <v>908.6869938484358</v>
+        <v>902.2058561117344</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1278567662094823</v>
+        <v>0.1291415461077801</v>
       </c>
       <c r="T47">
-        <v>1.89507543208966</v>
+        <v>1.924747023274366</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.136929990173117</v>
+        <v>2.090474990386745</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09186862649820124</v>
+        <v>0.09176497458118721</v>
       </c>
       <c r="C48">
-        <v>7267.299569783673</v>
+        <v>7161.309341812802</v>
       </c>
       <c r="D48">
-        <v>12733.84305749513</v>
+        <v>12762.55812273538</v>
       </c>
       <c r="E48">
-        <v>2392.314166599595</v>
+        <v>2527.019459810713</v>
       </c>
       <c r="F48">
-        <v>6196.443487711457</v>
+        <v>6331.148780922575</v>
       </c>
       <c r="G48">
         <v>729.9</v>
@@ -5229,28 +5229,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M48">
-        <v>397.1920275623044</v>
+        <v>405.8266368571371</v>
       </c>
       <c r="N48">
-        <v>433.1279724376956</v>
+        <v>424.493363142863</v>
       </c>
       <c r="O48">
-        <v>108.0221163259613</v>
+        <v>105.86864476783</v>
       </c>
       <c r="P48">
-        <v>325.1058561117343</v>
+        <v>318.6247183750329</v>
       </c>
       <c r="Q48">
-        <v>902.2058561117344</v>
+        <v>895.7247183750329</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1291415461077801</v>
+        <v>0.1304748082663909</v>
       </c>
       <c r="T48">
-        <v>1.924747023274366</v>
+        <v>1.955538297145287</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.090474990386745</v>
+        <v>2.045996799101921</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09176497458118721</v>
+        <v>0.09166132266417315</v>
       </c>
       <c r="C49">
-        <v>7161.309341812802</v>
+        <v>7055.448912608588</v>
       </c>
       <c r="D49">
-        <v>12762.55812273538</v>
+        <v>12791.40298674228</v>
       </c>
       <c r="E49">
-        <v>2527.019459810713</v>
+        <v>2661.724753021832</v>
       </c>
       <c r="F49">
-        <v>6331.148780922575</v>
+        <v>6465.854074133695</v>
       </c>
       <c r="G49">
         <v>729.9</v>
@@ -5311,28 +5311,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M49">
-        <v>405.8266368571371</v>
+        <v>414.4612461519699</v>
       </c>
       <c r="N49">
-        <v>424.493363142863</v>
+        <v>415.8587538480302</v>
       </c>
       <c r="O49">
-        <v>105.86864476783</v>
+        <v>103.7151732096987</v>
       </c>
       <c r="P49">
-        <v>318.6247183750329</v>
+        <v>312.1435806383315</v>
       </c>
       <c r="Q49">
-        <v>895.7247183750329</v>
+        <v>889.2435806383314</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1304748082663909</v>
+        <v>0.1318593497387945</v>
       </c>
       <c r="T49">
-        <v>1.955538297145287</v>
+        <v>1.987513850780475</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.045996799101921</v>
+        <v>2.003371865787297</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09166132266417315</v>
+        <v>0.09586086054715912</v>
       </c>
       <c r="C50">
-        <v>7055.448912608589</v>
+        <v>5847.690123468056</v>
       </c>
       <c r="D50">
-        <v>12791.40298674228</v>
+        <v>11718.34949081287</v>
       </c>
       <c r="E50">
-        <v>2661.724753021831</v>
+        <v>2796.430046232949</v>
       </c>
       <c r="F50">
-        <v>6465.854074133694</v>
+        <v>6600.559367344812</v>
       </c>
       <c r="G50">
         <v>729.9</v>
@@ -5393,45 +5393,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M50">
-        <v>414.4612461519698</v>
+        <v>500.3224000447368</v>
       </c>
       <c r="N50">
-        <v>415.8587538480302</v>
+        <v>329.9975999552632</v>
       </c>
       <c r="O50">
-        <v>103.7151732096987</v>
+        <v>82.30140142884265</v>
       </c>
       <c r="P50">
-        <v>312.1435806383315</v>
+        <v>247.6961985264206</v>
       </c>
       <c r="Q50">
-        <v>889.2435806383315</v>
+        <v>824.7961985264205</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1318593497387945</v>
+        <v>0.133298186955214</v>
       </c>
       <c r="T50">
-        <v>1.987513850780474</v>
+        <v>2.020743347695473</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.04811346</v>
+        <v>0.05689548</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.003371865787297</v>
+        <v>1.659569909174077</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09586086054715912</v>
+        <v>0.0958450288301451</v>
       </c>
       <c r="C51">
-        <v>5847.690123468056</v>
+        <v>5716.691923595608</v>
       </c>
       <c r="D51">
-        <v>11718.34949081287</v>
+        <v>11722.05658415154</v>
       </c>
       <c r="E51">
-        <v>2796.430046232949</v>
+        <v>2931.135339444068</v>
       </c>
       <c r="F51">
-        <v>6600.559367344812</v>
+        <v>6735.264660555931</v>
       </c>
       <c r="G51">
         <v>729.9</v>
@@ -5475,28 +5475,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M51">
-        <v>500.3224000447368</v>
+        <v>510.5330612701396</v>
       </c>
       <c r="N51">
-        <v>329.9975999552632</v>
+        <v>319.7869387298604</v>
       </c>
       <c r="O51">
-        <v>82.30140142884265</v>
+        <v>79.75486251922719</v>
       </c>
       <c r="P51">
-        <v>247.6961985264206</v>
+        <v>240.0320762106332</v>
       </c>
       <c r="Q51">
-        <v>824.7961985264205</v>
+        <v>817.1320762106333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.133298186955214</v>
+        <v>0.1347945776602902</v>
       </c>
       <c r="T51">
-        <v>2.020743347695473</v>
+        <v>2.055302024487072</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.659569909174077</v>
+        <v>1.626378510990595</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0958450288301451</v>
+        <v>0.09582919711313106</v>
       </c>
       <c r="C52">
-        <v>5716.691923595608</v>
+        <v>5585.696069939219</v>
       </c>
       <c r="D52">
-        <v>11722.05658415154</v>
+        <v>11725.76602370627</v>
       </c>
       <c r="E52">
-        <v>2931.135339444068</v>
+        <v>3065.840632655188</v>
       </c>
       <c r="F52">
-        <v>6735.264660555931</v>
+        <v>6869.96995376705</v>
       </c>
       <c r="G52">
         <v>729.9</v>
@@ -5557,28 +5557,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M52">
-        <v>510.5330612701396</v>
+        <v>520.7437224955424</v>
       </c>
       <c r="N52">
-        <v>319.7869387298604</v>
+        <v>309.5762775044576</v>
       </c>
       <c r="O52">
-        <v>79.75486251922719</v>
+        <v>77.20832360961172</v>
       </c>
       <c r="P52">
-        <v>240.0320762106332</v>
+        <v>232.3679538948459</v>
       </c>
       <c r="Q52">
-        <v>817.1320762106333</v>
+        <v>809.4679538948459</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1347945776602902</v>
+        <v>0.1363520455370022</v>
       </c>
       <c r="T52">
-        <v>2.055302024487072</v>
+        <v>2.091271259515062</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.626378510990595</v>
+        <v>1.594488736265289</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09582919711313106</v>
+        <v>0.09581336539611703</v>
       </c>
       <c r="C53">
-        <v>5585.696069939219</v>
+        <v>5454.702564726967</v>
       </c>
       <c r="D53">
-        <v>11725.76602370627</v>
+        <v>11729.47781170514</v>
       </c>
       <c r="E53">
-        <v>3065.840632655188</v>
+        <v>3200.545925866306</v>
       </c>
       <c r="F53">
-        <v>6869.96995376705</v>
+        <v>7004.675246978169</v>
       </c>
       <c r="G53">
         <v>729.9</v>
@@ -5639,28 +5639,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M53">
-        <v>520.7437224955424</v>
+        <v>530.9543837209452</v>
       </c>
       <c r="N53">
-        <v>309.5762775044576</v>
+        <v>299.3656162790548</v>
       </c>
       <c r="O53">
-        <v>77.20832360961172</v>
+        <v>74.66178469999629</v>
       </c>
       <c r="P53">
-        <v>232.3679538948459</v>
+        <v>224.7038315790585</v>
       </c>
       <c r="Q53">
-        <v>809.4679538948459</v>
+        <v>801.8038315790586</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1363520455370022</v>
+        <v>0.1379744079085772</v>
       </c>
       <c r="T53">
-        <v>2.091271259515062</v>
+        <v>2.128739212669219</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.594488736265289</v>
+        <v>1.563825491337111</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09581336539611703</v>
+        <v>0.09579753367910301</v>
       </c>
       <c r="C54">
-        <v>5454.702564726967</v>
+        <v>5323.711410189744</v>
       </c>
       <c r="D54">
-        <v>11729.47781170514</v>
+        <v>11733.19195037903</v>
       </c>
       <c r="E54">
-        <v>3200.545925866306</v>
+        <v>3335.251219077425</v>
       </c>
       <c r="F54">
-        <v>7004.675246978169</v>
+        <v>7139.380540189288</v>
       </c>
       <c r="G54">
         <v>729.9</v>
@@ -5721,28 +5721,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M54">
-        <v>530.9543837209452</v>
+        <v>541.1650449463481</v>
       </c>
       <c r="N54">
-        <v>299.3656162790548</v>
+        <v>289.154955053652</v>
       </c>
       <c r="O54">
-        <v>74.66178469999629</v>
+        <v>72.11524579038081</v>
       </c>
       <c r="P54">
-        <v>224.7038315790585</v>
+        <v>217.0397092632712</v>
       </c>
       <c r="Q54">
-        <v>801.8038315790586</v>
+        <v>794.1397092632712</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1379744079085772</v>
+        <v>0.1396658069768149</v>
       </c>
       <c r="T54">
-        <v>2.128739212669219</v>
+        <v>2.167801546808659</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.563825491337111</v>
+        <v>1.534319349991127</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09579753367910301</v>
+        <v>0.09578170196208896</v>
       </c>
       <c r="C55">
-        <v>5323.711410189744</v>
+        <v>5192.722608561302</v>
       </c>
       <c r="D55">
-        <v>11733.19195037903</v>
+        <v>11736.90844196171</v>
       </c>
       <c r="E55">
-        <v>3335.251219077425</v>
+        <v>3469.956512288543</v>
       </c>
       <c r="F55">
-        <v>7139.380540189288</v>
+        <v>7274.085833400406</v>
       </c>
       <c r="G55">
         <v>729.9</v>
@@ -5803,28 +5803,28 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M55">
-        <v>541.1650449463481</v>
+        <v>551.3757061717508</v>
       </c>
       <c r="N55">
-        <v>289.154955053652</v>
+        <v>278.9442938282492</v>
       </c>
       <c r="O55">
-        <v>72.11524579038081</v>
+        <v>69.56870688076536</v>
       </c>
       <c r="P55">
-        <v>217.0397092632712</v>
+        <v>209.3755869474838</v>
       </c>
       <c r="Q55">
-        <v>794.1397092632712</v>
+        <v>786.4755869474839</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1396658069768149</v>
+        <v>0.141430745134976</v>
       </c>
       <c r="T55">
-        <v>2.167801546808659</v>
+        <v>2.208562243301987</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.534319349991127</v>
+        <v>1.505906028694996</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09578170196208896</v>
+        <v>0.1147142113355278</v>
       </c>
       <c r="C56">
-        <v>5192.722608561302</v>
+        <v>1833.586174279039</v>
       </c>
       <c r="D56">
-        <v>11736.90844196171</v>
+        <v>8512.477300890565</v>
       </c>
       <c r="E56">
-        <v>3469.956512288543</v>
+        <v>3604.661805499662</v>
       </c>
       <c r="F56">
-        <v>7274.085833400406</v>
+        <v>7408.791126611525</v>
       </c>
       <c r="G56">
         <v>729.9</v>
@@ -5885,45 +5885,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M56">
-        <v>551.3757061717508</v>
+        <v>878.682627616127</v>
       </c>
       <c r="N56">
-        <v>278.9442938282492</v>
+        <v>-48.36262761612693</v>
       </c>
       <c r="O56">
-        <v>69.56870688076536</v>
+        <v>-12.06163932746206</v>
       </c>
       <c r="P56">
-        <v>209.3755869474838</v>
+        <v>-36.30098828866487</v>
       </c>
       <c r="Q56">
-        <v>786.4755869474839</v>
+        <v>540.7990117113352</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.141430745134976</v>
+        <v>0.1441270308440529</v>
       </c>
       <c r="T56">
-        <v>2.208562243301987</v>
+        <v>2.270832121109766</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.2494</v>
+        <v>0.2356730422243747</v>
       </c>
       <c r="W56">
-        <v>0.05689548</v>
+        <v>0.09064917719218916</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.505906028694996</v>
+        <v>0.9449600730728738</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1147142113355278</v>
+        <v>0.1154422113355278</v>
       </c>
       <c r="C57">
-        <v>1833.586174279039</v>
+        <v>1609.896293183551</v>
       </c>
       <c r="D57">
-        <v>8512.477300890565</v>
+        <v>8423.492713006195</v>
       </c>
       <c r="E57">
-        <v>3604.661805499662</v>
+        <v>3739.367098710781</v>
       </c>
       <c r="F57">
-        <v>7408.791126611525</v>
+        <v>7543.496419822643</v>
       </c>
       <c r="G57">
         <v>729.9</v>
@@ -5967,37 +5967,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M57">
-        <v>878.682627616127</v>
+        <v>894.6586753909656</v>
       </c>
       <c r="N57">
-        <v>-48.36262761612693</v>
+        <v>-64.33867539096559</v>
       </c>
       <c r="O57">
-        <v>-12.06163932746206</v>
+        <v>-16.04606564250682</v>
       </c>
       <c r="P57">
-        <v>-36.30098828866487</v>
+        <v>-48.29260974845877</v>
       </c>
       <c r="Q57">
-        <v>540.7990117113352</v>
+        <v>528.8073902515413</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1441270308440529</v>
+        <v>0.1463617360905086</v>
       </c>
       <c r="T57">
-        <v>2.270832121109766</v>
+        <v>2.322441942044079</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.2356730422243747</v>
+        <v>0.2314645950417966</v>
       </c>
       <c r="W57">
-        <v>0.09064917719218916</v>
+        <v>0.09114829902804293</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9449600730728738</v>
+        <v>0.9280857860537153</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1154422113355278</v>
+        <v>0.1161702113355278</v>
       </c>
       <c r="C58">
-        <v>1609.896293183551</v>
+        <v>1388.047554206303</v>
       </c>
       <c r="D58">
-        <v>8423.492713006195</v>
+        <v>8336.349267240066</v>
       </c>
       <c r="E58">
-        <v>3739.367098710781</v>
+        <v>3874.0723919219</v>
       </c>
       <c r="F58">
-        <v>7543.496419822643</v>
+        <v>7678.201713033763</v>
       </c>
       <c r="G58">
         <v>729.9</v>
@@ -6049,37 +6049,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M58">
-        <v>894.6586753909656</v>
+        <v>910.6347231658043</v>
       </c>
       <c r="N58">
-        <v>-64.33867539096559</v>
+        <v>-80.31472316580425</v>
       </c>
       <c r="O58">
-        <v>-16.04606564250682</v>
+        <v>-20.03049195755158</v>
       </c>
       <c r="P58">
-        <v>-48.29260974845877</v>
+        <v>-60.28423120825267</v>
       </c>
       <c r="Q58">
-        <v>528.8073902515413</v>
+        <v>516.8157687917474</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1463617360905086</v>
+        <v>0.1487003811158693</v>
       </c>
       <c r="T58">
-        <v>2.322441942044079</v>
+        <v>2.376452219766034</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.2314645950417966</v>
+        <v>0.2274038126726423</v>
       </c>
       <c r="W58">
-        <v>0.09114829902804293</v>
+        <v>0.09162990781702463</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9280857860537153</v>
+        <v>0.9118035792808431</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1161702113355278</v>
+        <v>0.1168982113355278</v>
       </c>
       <c r="C59">
-        <v>1388.047554206303</v>
+        <v>1167.983401010501</v>
       </c>
       <c r="D59">
-        <v>8336.349267240066</v>
+        <v>8250.990407255382</v>
       </c>
       <c r="E59">
-        <v>3874.0723919219</v>
+        <v>4008.777685133018</v>
       </c>
       <c r="F59">
-        <v>7678.201713033763</v>
+        <v>7812.907006244881</v>
       </c>
       <c r="G59">
         <v>729.9</v>
@@ -6131,37 +6131,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M59">
-        <v>910.6347231658043</v>
+        <v>926.610770940643</v>
       </c>
       <c r="N59">
-        <v>-80.31472316580425</v>
+        <v>-96.29077094064291</v>
       </c>
       <c r="O59">
-        <v>-20.03049195755158</v>
+        <v>-24.01491827259634</v>
       </c>
       <c r="P59">
-        <v>-60.28423120825267</v>
+        <v>-72.27585266804657</v>
       </c>
       <c r="Q59">
-        <v>516.8157687917474</v>
+        <v>504.8241473319534</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1487003811158693</v>
+        <v>0.1511503901900567</v>
       </c>
       <c r="T59">
-        <v>2.376452219766034</v>
+        <v>2.43303441547475</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.2274038126726423</v>
+        <v>0.2234830572817346</v>
       </c>
       <c r="W59">
-        <v>0.09162990781702463</v>
+        <v>0.09209490940638627</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9118035792808431</v>
+        <v>0.896082827913932</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1168982113355278</v>
+        <v>0.1176262113355278</v>
       </c>
       <c r="C60">
-        <v>1167.983401010503</v>
+        <v>949.6495701834674</v>
       </c>
       <c r="D60">
-        <v>8250.990407255384</v>
+        <v>8167.361869639466</v>
       </c>
       <c r="E60">
-        <v>4008.777685133017</v>
+        <v>4143.482978344136</v>
       </c>
       <c r="F60">
-        <v>7812.90700624488</v>
+        <v>7947.612299455998</v>
       </c>
       <c r="G60">
         <v>729.9</v>
@@ -6213,37 +6213,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M60">
-        <v>926.6107709406429</v>
+        <v>942.5868187154815</v>
       </c>
       <c r="N60">
-        <v>-96.2907709406428</v>
+        <v>-112.2668187154815</v>
       </c>
       <c r="O60">
-        <v>-24.01491827259632</v>
+        <v>-27.99934458764108</v>
       </c>
       <c r="P60">
-        <v>-72.27585266804648</v>
+        <v>-84.26747412784039</v>
       </c>
       <c r="Q60">
-        <v>504.8241473319536</v>
+        <v>492.8325258721596</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1511503901900566</v>
+        <v>0.1537199119020092</v>
       </c>
       <c r="T60">
-        <v>2.433034415474749</v>
+        <v>2.492376718291207</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.2234830572817347</v>
+        <v>0.2196952088532307</v>
       </c>
       <c r="W60">
-        <v>0.09209490940638627</v>
+        <v>0.09254414823000685</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8960828279139321</v>
+        <v>0.880894983373018</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1176262113355278</v>
+        <v>0.1183542113355278</v>
       </c>
       <c r="C61">
-        <v>949.6495701834674</v>
+        <v>732.9939762020604</v>
       </c>
       <c r="D61">
-        <v>8167.361869639466</v>
+        <v>8085.411568869178</v>
       </c>
       <c r="E61">
-        <v>4143.482978344136</v>
+        <v>4278.188271555255</v>
       </c>
       <c r="F61">
-        <v>7947.612299455998</v>
+        <v>8082.317592667117</v>
       </c>
       <c r="G61">
         <v>729.9</v>
@@ -6295,37 +6295,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M61">
-        <v>942.5868187154815</v>
+        <v>958.5628664903202</v>
       </c>
       <c r="N61">
-        <v>-112.2668187154815</v>
+        <v>-128.2428664903201</v>
       </c>
       <c r="O61">
-        <v>-27.99934458764108</v>
+        <v>-31.98377090268584</v>
       </c>
       <c r="P61">
-        <v>-84.26747412784039</v>
+        <v>-96.25909558763428</v>
       </c>
       <c r="Q61">
-        <v>492.8325258721596</v>
+        <v>480.8409044123657</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1537199119020092</v>
+        <v>0.1564179096995595</v>
       </c>
       <c r="T61">
-        <v>2.492376718291207</v>
+        <v>2.554686136248487</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.2196952088532307</v>
+        <v>0.2160336220390102</v>
       </c>
       <c r="W61">
-        <v>0.09254414823000685</v>
+        <v>0.0929784124261734</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.880894983373018</v>
+        <v>0.8662134003168011</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1183542113355278</v>
+        <v>0.1190822113355278</v>
       </c>
       <c r="C62">
-        <v>732.9939762020604</v>
+        <v>517.966603254752</v>
       </c>
       <c r="D62">
-        <v>8085.411568869178</v>
+        <v>8005.089489132987</v>
       </c>
       <c r="E62">
-        <v>4278.188271555255</v>
+        <v>4412.893564766373</v>
       </c>
       <c r="F62">
-        <v>8082.317592667117</v>
+        <v>8217.022885878236</v>
       </c>
       <c r="G62">
         <v>729.9</v>
@@ -6377,37 +6377,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M62">
-        <v>958.5628664903202</v>
+        <v>974.5389142651588</v>
       </c>
       <c r="N62">
-        <v>-128.2428664903201</v>
+        <v>-144.2189142651588</v>
       </c>
       <c r="O62">
-        <v>-31.98377090268584</v>
+        <v>-35.96819721773061</v>
       </c>
       <c r="P62">
-        <v>-96.25909558763428</v>
+        <v>-108.2507170474282</v>
       </c>
       <c r="Q62">
-        <v>480.8409044123657</v>
+        <v>468.8492829525719</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1564179096995595</v>
+        <v>0.1592542663585225</v>
       </c>
       <c r="T62">
-        <v>2.554686136248487</v>
+        <v>2.620190908972807</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.2160336220390102</v>
+        <v>0.2124920872514854</v>
       </c>
       <c r="W62">
-        <v>0.0929784124261734</v>
+        <v>0.09339843845197383</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8662134003168011</v>
+        <v>0.8520131806394765</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1190822113355278</v>
+        <v>0.1198102113355278</v>
       </c>
       <c r="C63">
-        <v>517.966603254752</v>
+        <v>304.5194034482211</v>
       </c>
       <c r="D63">
-        <v>8005.089489132987</v>
+        <v>7926.347582537575</v>
       </c>
       <c r="E63">
-        <v>4412.893564766373</v>
+        <v>4547.598857977491</v>
       </c>
       <c r="F63">
-        <v>8217.022885878236</v>
+        <v>8351.728179089354</v>
       </c>
       <c r="G63">
         <v>729.9</v>
@@ -6459,37 +6459,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M63">
-        <v>974.5389142651588</v>
+        <v>990.5149620399975</v>
       </c>
       <c r="N63">
-        <v>-144.2189142651588</v>
+        <v>-160.1949620399974</v>
       </c>
       <c r="O63">
-        <v>-35.96819721773061</v>
+        <v>-39.95262353277536</v>
       </c>
       <c r="P63">
-        <v>-108.2507170474282</v>
+        <v>-120.2423385072221</v>
       </c>
       <c r="Q63">
-        <v>468.8492829525719</v>
+        <v>456.8576614927779</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1592542663585225</v>
+        <v>0.1622399049469047</v>
       </c>
       <c r="T63">
-        <v>2.620190908972807</v>
+        <v>2.689143301314196</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.2124920872514854</v>
+        <v>0.2090647955216228</v>
       </c>
       <c r="W63">
-        <v>0.09339843845197383</v>
+        <v>0.09380491525113556</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8520131806394765</v>
+        <v>0.8382710325646462</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1198102113355278</v>
+        <v>0.1205382113355278</v>
       </c>
       <c r="C64">
-        <v>304.5194034482211</v>
+        <v>92.60620096319872</v>
       </c>
       <c r="D64">
-        <v>7926.347582537575</v>
+        <v>7849.139673263673</v>
       </c>
       <c r="E64">
-        <v>4547.598857977491</v>
+        <v>4682.304151188611</v>
       </c>
       <c r="F64">
-        <v>8351.728179089354</v>
+        <v>8486.433472300474</v>
       </c>
       <c r="G64">
         <v>729.9</v>
@@ -6541,37 +6541,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M64">
-        <v>990.5149620399975</v>
+        <v>1006.491009814836</v>
       </c>
       <c r="N64">
-        <v>-160.1949620399974</v>
+        <v>-176.1710098148362</v>
       </c>
       <c r="O64">
-        <v>-39.95262353277536</v>
+        <v>-43.93704984782016</v>
       </c>
       <c r="P64">
-        <v>-120.2423385072221</v>
+        <v>-132.2339599670161</v>
       </c>
       <c r="Q64">
-        <v>456.8576614927779</v>
+        <v>444.866040032984</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1622399049469047</v>
+        <v>0.1653869294049291</v>
       </c>
       <c r="T64">
-        <v>2.689143301314196</v>
+        <v>2.761822849998364</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.2090647955216228</v>
+        <v>0.2057463067038192</v>
       </c>
       <c r="W64">
-        <v>0.09380491525113556</v>
+        <v>0.09419848802492704</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8382710325646462</v>
+        <v>0.824965143158858</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1205382113355278</v>
+        <v>0.1212662113355278</v>
       </c>
       <c r="C65">
-        <v>92.60620096319872</v>
+        <v>-117.8173982422468</v>
       </c>
       <c r="D65">
-        <v>7849.139673263673</v>
+        <v>7773.421367269345</v>
       </c>
       <c r="E65">
-        <v>4682.304151188611</v>
+        <v>4817.00944439973</v>
       </c>
       <c r="F65">
-        <v>8486.433472300474</v>
+        <v>8621.138765511592</v>
       </c>
       <c r="G65">
         <v>729.9</v>
@@ -6623,37 +6623,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M65">
-        <v>1006.491009814836</v>
+        <v>1022.467057589675</v>
       </c>
       <c r="N65">
-        <v>-176.1710098148362</v>
+        <v>-192.1470575896749</v>
       </c>
       <c r="O65">
-        <v>-43.93704984782016</v>
+        <v>-47.92147616286492</v>
       </c>
       <c r="P65">
-        <v>-132.2339599670161</v>
+        <v>-144.22558142681</v>
       </c>
       <c r="Q65">
-        <v>444.866040032984</v>
+        <v>432.87441857319</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1653869294049291</v>
+        <v>0.1687087885550661</v>
       </c>
       <c r="T65">
-        <v>2.761822849998364</v>
+        <v>2.838540151387207</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.2057463067038192</v>
+        <v>0.202531520661572</v>
       </c>
       <c r="W65">
-        <v>0.09419848802492704</v>
+        <v>0.09457976164953756</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.824965143158858</v>
+        <v>0.8120750627970009</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1212662113355278</v>
+        <v>0.1781216857172215</v>
       </c>
       <c r="C66">
-        <v>-117.8173982422468</v>
+        <v>-3592.576568558498</v>
       </c>
       <c r="D66">
-        <v>7773.421367269345</v>
+        <v>4433.367490164213</v>
       </c>
       <c r="E66">
-        <v>4817.00944439973</v>
+        <v>4951.714737610848</v>
       </c>
       <c r="F66">
-        <v>8621.138765511592</v>
+        <v>8755.844058722711</v>
       </c>
       <c r="G66">
         <v>729.9</v>
@@ -6705,45 +6705,45 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M66">
-        <v>1022.467057589675</v>
+        <v>1758.17348699152</v>
       </c>
       <c r="N66">
-        <v>-192.1470575896749</v>
+        <v>-927.8534869915203</v>
       </c>
       <c r="O66">
-        <v>-47.92147616286492</v>
+        <v>-231.4066596556852</v>
       </c>
       <c r="P66">
-        <v>-144.22558142681</v>
+        <v>-696.4468273358351</v>
       </c>
       <c r="Q66">
-        <v>432.87441857319</v>
+        <v>-119.3468273358351</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1687087885550661</v>
+        <v>0.1799275378900498</v>
       </c>
       <c r="T66">
-        <v>2.838540151387207</v>
+        <v>3.097633669516162</v>
       </c>
       <c r="U66">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.202531520661572</v>
+        <v>0.1177823517031563</v>
       </c>
       <c r="W66">
-        <v>0.09457976164953756</v>
+        <v>0.1771493037780062</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8120750627970009</v>
+        <v>0.4722628376229203</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1781216857172215</v>
+        <v>0.1796716857172215</v>
       </c>
       <c r="C67">
-        <v>-3592.576568558498</v>
+        <v>-3778.612504040527</v>
       </c>
       <c r="D67">
-        <v>4433.367490164213</v>
+        <v>4382.036847893302</v>
       </c>
       <c r="E67">
-        <v>4951.714737610848</v>
+        <v>5086.420030821966</v>
       </c>
       <c r="F67">
-        <v>8755.844058722711</v>
+        <v>8890.549351933829</v>
       </c>
       <c r="G67">
         <v>729.9</v>
@@ -6787,37 +6787,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M67">
-        <v>1758.17348699152</v>
+        <v>1785.222309868313</v>
       </c>
       <c r="N67">
-        <v>-927.8534869915203</v>
+        <v>-954.9023098683127</v>
       </c>
       <c r="O67">
-        <v>-231.4066596556852</v>
+        <v>-238.1526360811572</v>
       </c>
       <c r="P67">
-        <v>-696.4468273358351</v>
+        <v>-716.7496737871555</v>
       </c>
       <c r="Q67">
-        <v>-119.3468273358351</v>
+        <v>-139.6496737871555</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1799275378900498</v>
+        <v>0.1838724654750513</v>
       </c>
       <c r="T67">
-        <v>3.097633669516162</v>
+        <v>3.18874054214899</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1177823517031563</v>
+        <v>0.1159977706167449</v>
       </c>
       <c r="W67">
-        <v>0.1771493037780062</v>
+        <v>0.1775076476601576</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4722628376229203</v>
+        <v>0.4651073400831792</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1796716857172215</v>
+        <v>0.1812216857172215</v>
       </c>
       <c r="C68">
-        <v>-3778.612504040527</v>
+        <v>-3963.473406216798</v>
       </c>
       <c r="D68">
-        <v>4382.036847893302</v>
+        <v>4331.881238928151</v>
       </c>
       <c r="E68">
-        <v>5086.420030821966</v>
+        <v>5221.125324033086</v>
       </c>
       <c r="F68">
-        <v>8890.549351933829</v>
+        <v>9025.254645144949</v>
       </c>
       <c r="G68">
         <v>729.9</v>
@@ -6869,37 +6869,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M68">
-        <v>1785.222309868313</v>
+        <v>1812.271132745106</v>
       </c>
       <c r="N68">
-        <v>-954.9023098683127</v>
+        <v>-981.9511327451058</v>
       </c>
       <c r="O68">
-        <v>-238.1526360811572</v>
+        <v>-244.8986125066294</v>
       </c>
       <c r="P68">
-        <v>-716.7496737871555</v>
+        <v>-737.0525202384764</v>
       </c>
       <c r="Q68">
-        <v>-139.6496737871555</v>
+        <v>-159.9525202384764</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1838724654750513</v>
+        <v>0.1880564795803558</v>
       </c>
       <c r="T68">
-        <v>3.18874054214899</v>
+        <v>3.285369043426232</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1159977706167449</v>
+        <v>0.1142664606075397</v>
       </c>
       <c r="W68">
-        <v>0.1775076476601576</v>
+        <v>0.177855294710006</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4651073400831792</v>
+        <v>0.4581654394849226</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1812216857172215</v>
+        <v>0.1827716857172215</v>
       </c>
       <c r="C69">
-        <v>-3963.473406216798</v>
+        <v>-4147.199165848988</v>
       </c>
       <c r="D69">
-        <v>4331.881238928151</v>
+        <v>4282.86077250708</v>
       </c>
       <c r="E69">
-        <v>5221.125324033086</v>
+        <v>5355.830617244204</v>
       </c>
       <c r="F69">
-        <v>9025.254645144949</v>
+        <v>9159.959938356067</v>
       </c>
       <c r="G69">
         <v>729.9</v>
@@ -6951,37 +6951,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M69">
-        <v>1812.271132745106</v>
+        <v>1839.319955621898</v>
       </c>
       <c r="N69">
-        <v>-981.9511327451058</v>
+        <v>-1008.999955621898</v>
       </c>
       <c r="O69">
-        <v>-244.8986125066294</v>
+        <v>-251.6445889321014</v>
       </c>
       <c r="P69">
-        <v>-737.0525202384764</v>
+        <v>-757.3553666897968</v>
       </c>
       <c r="Q69">
-        <v>-159.9525202384764</v>
+        <v>-180.2553666897968</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1880564795803558</v>
+        <v>0.192501994567242</v>
       </c>
       <c r="T69">
-        <v>3.285369043426232</v>
+        <v>3.388036826033302</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1142664606075397</v>
+        <v>0.1125860714809583</v>
       </c>
       <c r="W69">
-        <v>0.177855294710006</v>
+        <v>0.1781927168466236</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4581654394849226</v>
+        <v>0.4514277124336739</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1827716857172215</v>
+        <v>0.1843216857172215</v>
       </c>
       <c r="C70">
-        <v>-4147.199165848988</v>
+        <v>-4329.827888254707</v>
       </c>
       <c r="D70">
-        <v>4282.86077250708</v>
+        <v>4234.937343312478</v>
       </c>
       <c r="E70">
-        <v>5355.830617244204</v>
+        <v>5490.535910455323</v>
       </c>
       <c r="F70">
-        <v>9159.959938356067</v>
+        <v>9294.665231567185</v>
       </c>
       <c r="G70">
         <v>729.9</v>
@@ -7033,37 +7033,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M70">
-        <v>1839.319955621898</v>
+        <v>1866.368778498691</v>
       </c>
       <c r="N70">
-        <v>-1008.999955621898</v>
+        <v>-1036.048778498691</v>
       </c>
       <c r="O70">
-        <v>-251.6445889321014</v>
+        <v>-258.3905653575735</v>
       </c>
       <c r="P70">
-        <v>-757.3553666897968</v>
+        <v>-777.6582131411174</v>
       </c>
       <c r="Q70">
-        <v>-180.2553666897968</v>
+        <v>-200.5582131411173</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.192501994567242</v>
+        <v>0.1972343169726369</v>
       </c>
       <c r="T70">
-        <v>3.388036826033302</v>
+        <v>3.497328336550505</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1125860714809583</v>
+        <v>0.1109543892855821</v>
       </c>
       <c r="W70">
-        <v>0.1781927168466236</v>
+        <v>0.1785203586314551</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4514277124336739</v>
+        <v>0.4448852818186931</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1843216857172215</v>
+        <v>0.1858716857172215</v>
       </c>
       <c r="C71">
-        <v>-4329.827888254707</v>
+        <v>-4511.395992093993</v>
       </c>
       <c r="D71">
-        <v>4234.937343312478</v>
+        <v>4188.074532684311</v>
       </c>
       <c r="E71">
-        <v>5490.535910455323</v>
+        <v>5625.241203666441</v>
       </c>
       <c r="F71">
-        <v>9294.665231567185</v>
+        <v>9429.370524778304</v>
       </c>
       <c r="G71">
         <v>729.9</v>
@@ -7115,37 +7115,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M71">
-        <v>1866.368778498691</v>
+        <v>1893.417601375483</v>
       </c>
       <c r="N71">
-        <v>-1036.048778498691</v>
+        <v>-1063.097601375483</v>
       </c>
       <c r="O71">
-        <v>-258.3905653575735</v>
+        <v>-265.1365417830456</v>
       </c>
       <c r="P71">
-        <v>-777.6582131411174</v>
+        <v>-797.9610595924379</v>
       </c>
       <c r="Q71">
-        <v>-200.5582131411173</v>
+        <v>-220.8610595924379</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1972343169726369</v>
+        <v>0.2022821275383914</v>
       </c>
       <c r="T71">
-        <v>3.497328336550505</v>
+        <v>3.613905947768855</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1109543892855821</v>
+        <v>0.1093693265815023</v>
       </c>
       <c r="W71">
-        <v>0.1785203586314551</v>
+        <v>0.1788386392224343</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4448852818186931</v>
+        <v>0.4385297777927117</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1858716857172215</v>
+        <v>0.1874216857172215</v>
       </c>
       <c r="C72">
-        <v>-4511.395992093993</v>
+        <v>-4691.938301668712</v>
       </c>
       <c r="D72">
-        <v>4188.074532684311</v>
+        <v>4142.237516320713</v>
       </c>
       <c r="E72">
-        <v>5625.241203666441</v>
+        <v>5759.946496877561</v>
       </c>
       <c r="F72">
-        <v>9429.370524778304</v>
+        <v>9564.075817989424</v>
       </c>
       <c r="G72">
         <v>729.9</v>
@@ -7197,37 +7197,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M72">
-        <v>1893.417601375483</v>
+        <v>1920.466424252276</v>
       </c>
       <c r="N72">
-        <v>-1063.097601375483</v>
+        <v>-1090.146424252276</v>
       </c>
       <c r="O72">
-        <v>-265.1365417830456</v>
+        <v>-271.8825182085177</v>
       </c>
       <c r="P72">
-        <v>-797.9610595924379</v>
+        <v>-818.2639060437584</v>
       </c>
       <c r="Q72">
-        <v>-220.8610595924379</v>
+        <v>-241.1639060437584</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2022821275383914</v>
+        <v>0.2076780629707498</v>
       </c>
       <c r="T72">
-        <v>3.613905947768855</v>
+        <v>3.738523394243644</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1093693265815023</v>
+        <v>0.1078289135310586</v>
       </c>
       <c r="W72">
-        <v>0.1788386392224343</v>
+        <v>0.1791479541629634</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4385297777927117</v>
+        <v>0.4323533020491525</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1874216857172215</v>
+        <v>0.1889716857172215</v>
       </c>
       <c r="C73">
-        <v>-4691.93830166871</v>
+        <v>-4871.488133226455</v>
       </c>
       <c r="D73">
-        <v>4142.237516320713</v>
+        <v>4097.392977974086</v>
       </c>
       <c r="E73">
-        <v>5759.946496877559</v>
+        <v>5894.651790088677</v>
       </c>
       <c r="F73">
-        <v>9564.075817989422</v>
+        <v>9698.78111120054</v>
       </c>
       <c r="G73">
         <v>729.9</v>
@@ -7279,37 +7279,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M73">
-        <v>1920.466424252276</v>
+        <v>1947.515247129068</v>
       </c>
       <c r="N73">
-        <v>-1090.146424252276</v>
+        <v>-1117.195247129068</v>
       </c>
       <c r="O73">
-        <v>-271.8825182085177</v>
+        <v>-278.6284946339896</v>
       </c>
       <c r="P73">
-        <v>-818.2639060437584</v>
+        <v>-838.5667524950786</v>
       </c>
       <c r="Q73">
-        <v>-241.1639060437584</v>
+        <v>-261.4667524950786</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2076780629707497</v>
+        <v>0.2134594223625622</v>
       </c>
       <c r="T73">
-        <v>3.738523394243643</v>
+        <v>3.872042086895201</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1078289135310586</v>
+        <v>0.1063312897320162</v>
       </c>
       <c r="W73">
-        <v>0.1791479541629634</v>
+        <v>0.1794486770218112</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4323533020491523</v>
+        <v>0.4263483950762477</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1889716857172215</v>
+        <v>0.1905216857172214</v>
       </c>
       <c r="C74">
-        <v>-4871.488133226455</v>
+        <v>-5050.077375718464</v>
       </c>
       <c r="D74">
-        <v>4097.392977974086</v>
+        <v>4053.509028693195</v>
       </c>
       <c r="E74">
-        <v>5894.651790088677</v>
+        <v>6029.357083299796</v>
       </c>
       <c r="F74">
-        <v>9698.78111120054</v>
+        <v>9833.486404411658</v>
       </c>
       <c r="G74">
         <v>729.9</v>
@@ -7361,37 +7361,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M74">
-        <v>1947.515247129068</v>
+        <v>1974.564070005861</v>
       </c>
       <c r="N74">
-        <v>-1117.195247129068</v>
+        <v>-1144.244070005861</v>
       </c>
       <c r="O74">
-        <v>-278.6284946339896</v>
+        <v>-285.3744710594617</v>
       </c>
       <c r="P74">
-        <v>-838.5667524950786</v>
+        <v>-858.8695989463993</v>
       </c>
       <c r="Q74">
-        <v>-261.4667524950786</v>
+        <v>-281.7695989463992</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2134594223625622</v>
+        <v>0.2196690305982127</v>
       </c>
       <c r="T74">
-        <v>3.872042086895201</v>
+        <v>4.015451053076505</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1063312897320162</v>
+        <v>0.1048746967219885</v>
       </c>
       <c r="W74">
-        <v>0.1794486770218112</v>
+        <v>0.1797411608982247</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4263483950762477</v>
+        <v>0.4205080061026004</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1905216857172214</v>
+        <v>0.1920716857172215</v>
       </c>
       <c r="C75">
-        <v>-5050.077375718464</v>
+        <v>-5227.736566422918</v>
       </c>
       <c r="D75">
-        <v>4053.509028693195</v>
+        <v>4010.555131199861</v>
       </c>
       <c r="E75">
-        <v>6029.357083299796</v>
+        <v>6164.062376510916</v>
       </c>
       <c r="F75">
-        <v>9833.486404411658</v>
+        <v>9968.191697622779</v>
       </c>
       <c r="G75">
         <v>729.9</v>
@@ -7443,37 +7443,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M75">
-        <v>1974.564070005861</v>
+        <v>2001.612892882654</v>
       </c>
       <c r="N75">
-        <v>-1144.244070005861</v>
+        <v>-1171.292892882654</v>
       </c>
       <c r="O75">
-        <v>-285.3744710594617</v>
+        <v>-292.1204474849339</v>
       </c>
       <c r="P75">
-        <v>-858.8695989463993</v>
+        <v>-879.1724453977201</v>
       </c>
       <c r="Q75">
-        <v>-281.7695989463992</v>
+        <v>-302.0724453977201</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2196690305982127</v>
+        <v>0.2263563010058362</v>
       </c>
       <c r="T75">
-        <v>4.015451053076505</v>
+        <v>4.169891478194832</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1048746967219885</v>
+        <v>0.1034574710906103</v>
       </c>
       <c r="W75">
-        <v>0.1797411608982247</v>
+        <v>0.1800257398050054</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4205080061026004</v>
+        <v>0.4148254654795921</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1920716857172215</v>
+        <v>0.1936216857172214</v>
       </c>
       <c r="C76">
-        <v>-5227.736566422918</v>
+        <v>-5404.494961810475</v>
       </c>
       <c r="D76">
-        <v>4010.555131199861</v>
+        <v>3968.502029023422</v>
       </c>
       <c r="E76">
-        <v>6164.062376510916</v>
+        <v>6298.767669722034</v>
       </c>
       <c r="F76">
-        <v>9968.191697622779</v>
+        <v>10102.8969908339</v>
       </c>
       <c r="G76">
         <v>729.9</v>
@@ -7525,37 +7525,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M76">
-        <v>2001.612892882654</v>
+        <v>2028.661715759446</v>
       </c>
       <c r="N76">
-        <v>-1171.292892882654</v>
+        <v>-1198.341715759446</v>
       </c>
       <c r="O76">
-        <v>-292.1204474849339</v>
+        <v>-298.8664239104059</v>
       </c>
       <c r="P76">
-        <v>-879.1724453977201</v>
+        <v>-899.4752918490403</v>
       </c>
       <c r="Q76">
-        <v>-302.0724453977201</v>
+        <v>-322.3752918490403</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2263563010058362</v>
+        <v>0.2335785530460697</v>
       </c>
       <c r="T76">
-        <v>4.169891478194832</v>
+        <v>4.336687137322626</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1034574710906103</v>
+        <v>0.1020780381427355</v>
       </c>
       <c r="W76">
-        <v>0.1800257398050054</v>
+        <v>0.1803027299409387</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4148254654795921</v>
+        <v>0.4092944592731977</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1936216857172214</v>
+        <v>0.1951716857172215</v>
       </c>
       <c r="C77">
-        <v>-5404.494961810475</v>
+        <v>-5580.380603997712</v>
       </c>
       <c r="D77">
-        <v>3968.502029023422</v>
+        <v>3927.321680047303</v>
       </c>
       <c r="E77">
-        <v>6298.767669722034</v>
+        <v>6433.472962933152</v>
       </c>
       <c r="F77">
-        <v>10102.8969908339</v>
+        <v>10237.60228404502</v>
       </c>
       <c r="G77">
         <v>729.9</v>
@@ -7607,37 +7607,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M77">
-        <v>2028.661715759446</v>
+        <v>2055.710538636239</v>
       </c>
       <c r="N77">
-        <v>-1198.341715759446</v>
+        <v>-1225.390538636239</v>
       </c>
       <c r="O77">
-        <v>-298.8664239104059</v>
+        <v>-305.612400335878</v>
       </c>
       <c r="P77">
-        <v>-899.4752918490403</v>
+        <v>-919.778138300361</v>
       </c>
       <c r="Q77">
-        <v>-322.3752918490403</v>
+        <v>-342.678138300361</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2335785530460697</v>
+        <v>0.2414026594229893</v>
       </c>
       <c r="T77">
-        <v>4.336687137322626</v>
+        <v>4.517382434711069</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1020780381427355</v>
+        <v>0.10073490606191</v>
       </c>
       <c r="W77">
-        <v>0.1803027299409387</v>
+        <v>0.1805724308627685</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4092944592731977</v>
+        <v>0.4039090058617083</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1951716857172215</v>
+        <v>0.1967216857172215</v>
       </c>
       <c r="C78">
-        <v>-5580.380603997712</v>
+        <v>-5755.42038310557</v>
       </c>
       <c r="D78">
-        <v>3927.321680047303</v>
+        <v>3886.987194150565</v>
       </c>
       <c r="E78">
-        <v>6433.472962933152</v>
+        <v>6568.178256144272</v>
       </c>
       <c r="F78">
-        <v>10237.60228404502</v>
+        <v>10372.30757725614</v>
       </c>
       <c r="G78">
         <v>729.9</v>
@@ -7689,37 +7689,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M78">
-        <v>2055.710538636239</v>
+        <v>2082.759361513032</v>
       </c>
       <c r="N78">
-        <v>-1225.390538636239</v>
+        <v>-1252.439361513032</v>
       </c>
       <c r="O78">
-        <v>-305.612400335878</v>
+        <v>-312.3583767613502</v>
       </c>
       <c r="P78">
-        <v>-919.778138300361</v>
+        <v>-940.0809847516819</v>
       </c>
       <c r="Q78">
-        <v>-342.678138300361</v>
+        <v>-362.9809847516818</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2414026594229893</v>
+        <v>0.2499071228761627</v>
       </c>
       <c r="T78">
-        <v>4.517382434711069</v>
+        <v>4.713790366655028</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.10073490606191</v>
+        <v>0.09942666052863845</v>
       </c>
       <c r="W78">
-        <v>0.1805724308627685</v>
+        <v>0.1808351265658494</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4039090058617083</v>
+        <v>0.3986634343570107</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1967216857172215</v>
+        <v>0.1982716857172215</v>
       </c>
       <c r="C79">
-        <v>-5755.42038310557</v>
+        <v>-5929.640095814269</v>
       </c>
       <c r="D79">
-        <v>3886.987194150565</v>
+        <v>3847.472774652984</v>
       </c>
       <c r="E79">
-        <v>6568.178256144272</v>
+        <v>6702.883549355391</v>
       </c>
       <c r="F79">
-        <v>10372.30757725614</v>
+        <v>10507.01287046725</v>
       </c>
       <c r="G79">
         <v>729.9</v>
@@ -7771,37 +7771,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M79">
-        <v>2082.759361513032</v>
+        <v>2109.808184389824</v>
       </c>
       <c r="N79">
-        <v>-1252.439361513032</v>
+        <v>-1279.488184389824</v>
       </c>
       <c r="O79">
-        <v>-312.3583767613502</v>
+        <v>-319.1043531868222</v>
       </c>
       <c r="P79">
-        <v>-940.0809847516819</v>
+        <v>-960.383831203002</v>
       </c>
       <c r="Q79">
-        <v>-362.9809847516818</v>
+        <v>-383.283831203002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2499071228761627</v>
+        <v>0.2591847193705338</v>
       </c>
       <c r="T79">
-        <v>4.713790366655028</v>
+        <v>4.928053565139348</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09942666052863845</v>
+        <v>0.09815195975263029</v>
       </c>
       <c r="W79">
-        <v>0.1808351265658494</v>
+        <v>0.1810910864816719</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3986634343570107</v>
+        <v>0.393552364685767</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1982716857172215</v>
+        <v>0.1998216857172215</v>
       </c>
       <c r="C80">
-        <v>-5929.640095814269</v>
+        <v>-6103.064500382609</v>
       </c>
       <c r="D80">
-        <v>3847.472774652984</v>
+        <v>3808.753663295763</v>
       </c>
       <c r="E80">
-        <v>6702.883549355391</v>
+        <v>6837.588842566509</v>
       </c>
       <c r="F80">
-        <v>10507.01287046725</v>
+        <v>10641.71816367837</v>
       </c>
       <c r="G80">
         <v>729.9</v>
@@ -7853,37 +7853,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M80">
-        <v>2109.808184389824</v>
+        <v>2136.857007266617</v>
       </c>
       <c r="N80">
-        <v>-1279.488184389824</v>
+        <v>-1306.537007266617</v>
       </c>
       <c r="O80">
-        <v>-319.1043531868222</v>
+        <v>-325.8503296122943</v>
       </c>
       <c r="P80">
-        <v>-960.383831203002</v>
+        <v>-980.6866776543227</v>
       </c>
       <c r="Q80">
-        <v>-383.283831203002</v>
+        <v>-403.5866776543227</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2591847193705338</v>
+        <v>0.2693458964834163</v>
       </c>
       <c r="T80">
-        <v>4.928053565139348</v>
+        <v>5.162722782526936</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09815195975263029</v>
+        <v>0.09690952988234382</v>
       </c>
       <c r="W80">
-        <v>0.1810910864816719</v>
+        <v>0.1813405663996254</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.393552364685767</v>
+        <v>0.3885706891834155</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1998216857172215</v>
+        <v>0.2013716857172215</v>
       </c>
       <c r="C81">
-        <v>-6103.064500382609</v>
+        <v>-6275.717368378249</v>
       </c>
       <c r="D81">
-        <v>3808.753663295763</v>
+        <v>3770.80608851124</v>
       </c>
       <c r="E81">
-        <v>6837.588842566509</v>
+        <v>6972.294135777627</v>
       </c>
       <c r="F81">
-        <v>10641.71816367837</v>
+        <v>10776.42345688949</v>
       </c>
       <c r="G81">
         <v>729.9</v>
@@ -7935,37 +7935,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M81">
-        <v>2136.857007266617</v>
+        <v>2163.90583014341</v>
       </c>
       <c r="N81">
-        <v>-1306.537007266617</v>
+        <v>-1333.58583014341</v>
       </c>
       <c r="O81">
-        <v>-325.8503296122943</v>
+        <v>-332.5963060377663</v>
       </c>
       <c r="P81">
-        <v>-980.6866776543227</v>
+        <v>-1000.989524105643</v>
       </c>
       <c r="Q81">
-        <v>-403.5866776543227</v>
+        <v>-423.8895241056432</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2693458964834163</v>
+        <v>0.2805231913075872</v>
       </c>
       <c r="T81">
-        <v>5.162722782526936</v>
+        <v>5.420858921653283</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09690952988234382</v>
+        <v>0.09569816075881453</v>
       </c>
       <c r="W81">
-        <v>0.1813405663996254</v>
+        <v>0.1815838093196301</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3885706891834155</v>
+        <v>0.3837135555686229</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2013716857172215</v>
+        <v>0.2029216857172215</v>
       </c>
       <c r="C82">
-        <v>-6275.717368378249</v>
+        <v>-6447.621533346075</v>
       </c>
       <c r="D82">
-        <v>3770.80608851124</v>
+        <v>3733.607216754535</v>
       </c>
       <c r="E82">
-        <v>6972.294135777627</v>
+        <v>7106.999428988747</v>
       </c>
       <c r="F82">
-        <v>10776.42345688949</v>
+        <v>10911.12875010061</v>
       </c>
       <c r="G82">
         <v>729.9</v>
@@ -8017,37 +8017,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M82">
-        <v>2163.90583014341</v>
+        <v>2190.954653020202</v>
       </c>
       <c r="N82">
-        <v>-1333.58583014341</v>
+        <v>-1360.634653020202</v>
       </c>
       <c r="O82">
-        <v>-332.5963060377663</v>
+        <v>-339.3422824632385</v>
       </c>
       <c r="P82">
-        <v>-1000.989524105643</v>
+        <v>-1021.292370556964</v>
       </c>
       <c r="Q82">
-        <v>-423.8895241056432</v>
+        <v>-444.1923705569637</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2805231913075872</v>
+        <v>0.2928770434816707</v>
       </c>
       <c r="T82">
-        <v>5.420858921653283</v>
+        <v>5.706167285950825</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.09569816075881453</v>
+        <v>0.09451670198401434</v>
       </c>
       <c r="W82">
-        <v>0.1815838093196301</v>
+        <v>0.1818210462416099</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3837135555686229</v>
+        <v>0.3789763511788867</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2029216857172215</v>
+        <v>0.2044716857172215</v>
       </c>
       <c r="C83">
-        <v>-6447.621533346075</v>
+        <v>-6618.798936624034</v>
       </c>
       <c r="D83">
-        <v>3733.607216754535</v>
+        <v>3697.135106687694</v>
       </c>
       <c r="E83">
-        <v>7106.999428988747</v>
+        <v>7241.704722199866</v>
       </c>
       <c r="F83">
-        <v>10911.12875010061</v>
+        <v>11045.83404331173</v>
       </c>
       <c r="G83">
         <v>729.9</v>
@@ -8099,37 +8099,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M83">
-        <v>2190.954653020202</v>
+        <v>2218.003475896995</v>
       </c>
       <c r="N83">
-        <v>-1360.634653020202</v>
+        <v>-1387.683475896995</v>
       </c>
       <c r="O83">
-        <v>-339.3422824632385</v>
+        <v>-346.0882588887105</v>
       </c>
       <c r="P83">
-        <v>-1021.292370556964</v>
+        <v>-1041.595217008284</v>
       </c>
       <c r="Q83">
-        <v>-444.1923705569637</v>
+        <v>-464.4952170082844</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2928770434816707</v>
+        <v>0.3066035458973191</v>
       </c>
       <c r="T83">
-        <v>5.706167285950825</v>
+        <v>6.02317657961476</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.09451670198401434</v>
+        <v>0.09336405927689222</v>
       </c>
       <c r="W83">
-        <v>0.1818210462416099</v>
+        <v>0.1820524968972</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3789763511788867</v>
+        <v>0.374354688359632</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2044716857172215</v>
+        <v>0.2060216857172215</v>
       </c>
       <c r="C84">
-        <v>-6618.798936624034</v>
+        <v>-6789.270670499619</v>
       </c>
       <c r="D84">
-        <v>3697.135106687694</v>
+        <v>3661.368666023227</v>
       </c>
       <c r="E84">
-        <v>7241.704722199866</v>
+        <v>7376.410015410984</v>
       </c>
       <c r="F84">
-        <v>11045.83404331173</v>
+        <v>11180.53933652285</v>
       </c>
       <c r="G84">
         <v>729.9</v>
@@ -8181,37 +8181,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M84">
-        <v>2218.003475896995</v>
+        <v>2245.052298773788</v>
       </c>
       <c r="N84">
-        <v>-1387.683475896995</v>
+        <v>-1414.732298773788</v>
       </c>
       <c r="O84">
-        <v>-346.0882588887105</v>
+        <v>-352.8342353141826</v>
       </c>
       <c r="P84">
-        <v>-1041.595217008284</v>
+        <v>-1061.898063459605</v>
       </c>
       <c r="Q84">
-        <v>-464.4952170082844</v>
+        <v>-484.7980634596048</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3066035458973191</v>
+        <v>0.3219449309501026</v>
       </c>
       <c r="T84">
-        <v>6.02317657961476</v>
+        <v>6.377481084297981</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09336405927689222</v>
+        <v>0.09223919109283328</v>
       </c>
       <c r="W84">
-        <v>0.1820524968972</v>
+        <v>0.1822783704285591</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.374354688359632</v>
+        <v>0.3698443909095159</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2060216857172215</v>
+        <v>0.2075716857172215</v>
       </c>
       <c r="C85">
-        <v>-6789.270670499619</v>
+        <v>-6959.057018885351</v>
       </c>
       <c r="D85">
-        <v>3661.368666023227</v>
+        <v>3626.287610848614</v>
       </c>
       <c r="E85">
-        <v>7376.410015410984</v>
+        <v>7511.115308622102</v>
       </c>
       <c r="F85">
-        <v>11180.53933652285</v>
+        <v>11315.24462973396</v>
       </c>
       <c r="G85">
         <v>729.9</v>
@@ -8263,37 +8263,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M85">
-        <v>2245.052298773788</v>
+        <v>2272.10112165058</v>
       </c>
       <c r="N85">
-        <v>-1414.732298773788</v>
+        <v>-1441.78112165058</v>
       </c>
       <c r="O85">
-        <v>-352.8342353141826</v>
+        <v>-359.5802117396547</v>
       </c>
       <c r="P85">
-        <v>-1061.898063459605</v>
+        <v>-1082.200909910925</v>
       </c>
       <c r="Q85">
-        <v>-484.7980634596048</v>
+        <v>-505.1009099109255</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3219449309501026</v>
+        <v>0.3392039891344841</v>
       </c>
       <c r="T85">
-        <v>6.377481084297981</v>
+        <v>6.776073652066606</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09223919109283328</v>
+        <v>0.09114110548458525</v>
       </c>
       <c r="W85">
-        <v>0.1822783704285591</v>
+        <v>0.1824988660186953</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3698443909095159</v>
+        <v>0.3654414814939265</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2075716857172215</v>
+        <v>0.2091216857172215</v>
       </c>
       <c r="C86">
-        <v>-6959.057018885351</v>
+        <v>-7128.177495678074</v>
       </c>
       <c r="D86">
-        <v>3626.287610848614</v>
+        <v>3591.87242726701</v>
       </c>
       <c r="E86">
-        <v>7511.115308622102</v>
+        <v>7645.82060183322</v>
       </c>
       <c r="F86">
-        <v>11315.24462973396</v>
+        <v>11449.94992294508</v>
       </c>
       <c r="G86">
         <v>729.9</v>
@@ -8345,37 +8345,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M86">
-        <v>2272.10112165058</v>
+        <v>2299.149944527373</v>
       </c>
       <c r="N86">
-        <v>-1441.78112165058</v>
+        <v>-1468.829944527372</v>
       </c>
       <c r="O86">
-        <v>-359.5802117396547</v>
+        <v>-366.3261881651267</v>
       </c>
       <c r="P86">
-        <v>-1082.200909910925</v>
+        <v>-1102.503756362246</v>
       </c>
       <c r="Q86">
-        <v>-505.1009099109255</v>
+        <v>-525.4037563622456</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3392039891344839</v>
+        <v>0.3587642550767828</v>
       </c>
       <c r="T86">
-        <v>6.776073652066603</v>
+        <v>7.227811895537709</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09114110548458525</v>
+        <v>0.09006885718476663</v>
       </c>
       <c r="W86">
-        <v>0.1824988660186953</v>
+        <v>0.1827141734772989</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3654414814939265</v>
+        <v>0.3611421699469392</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2091216857172215</v>
+        <v>0.2106716857172215</v>
       </c>
       <c r="C87">
-        <v>-7128.177495678074</v>
+        <v>-7296.650880954513</v>
       </c>
       <c r="D87">
-        <v>3591.87242726701</v>
+        <v>3558.104335201688</v>
       </c>
       <c r="E87">
-        <v>7645.82060183322</v>
+        <v>7780.525895044339</v>
       </c>
       <c r="F87">
-        <v>11449.94992294508</v>
+        <v>11584.6552161562</v>
       </c>
       <c r="G87">
         <v>729.9</v>
@@ -8427,37 +8427,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M87">
-        <v>2299.149944527373</v>
+        <v>2326.198767404165</v>
       </c>
       <c r="N87">
-        <v>-1468.829944527372</v>
+        <v>-1495.878767404165</v>
       </c>
       <c r="O87">
-        <v>-366.3261881651267</v>
+        <v>-373.0721645905988</v>
       </c>
       <c r="P87">
-        <v>-1102.503756362246</v>
+        <v>-1122.806602813566</v>
       </c>
       <c r="Q87">
-        <v>-525.4037563622456</v>
+        <v>-545.7066028135663</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3587642550767828</v>
+        <v>0.3811188447251244</v>
       </c>
       <c r="T87">
-        <v>7.227811895537709</v>
+        <v>7.744084173790402</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09006885718476663</v>
+        <v>0.0890215448919205</v>
       </c>
       <c r="W87">
-        <v>0.1827141734772989</v>
+        <v>0.1829244737857024</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3611421699469392</v>
+        <v>0.3569428423894166</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2106716857172215</v>
+        <v>0.2122216857172215</v>
       </c>
       <c r="C88">
-        <v>-7296.650880954513</v>
+        <v>-7464.495255144138</v>
       </c>
       <c r="D88">
-        <v>3558.104335201688</v>
+        <v>3524.965254223181</v>
       </c>
       <c r="E88">
-        <v>7780.525895044339</v>
+        <v>7915.231188255457</v>
       </c>
       <c r="F88">
-        <v>11584.6552161562</v>
+        <v>11719.36050936732</v>
       </c>
       <c r="G88">
         <v>729.9</v>
@@ -8509,37 +8509,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M88">
-        <v>2326.198767404165</v>
+        <v>2353.247590280958</v>
       </c>
       <c r="N88">
-        <v>-1495.878767404165</v>
+        <v>-1522.927590280958</v>
       </c>
       <c r="O88">
-        <v>-373.0721645905988</v>
+        <v>-379.8181410160709</v>
       </c>
       <c r="P88">
-        <v>-1122.806602813566</v>
+        <v>-1143.109449264887</v>
       </c>
       <c r="Q88">
-        <v>-545.7066028135663</v>
+        <v>-566.0094492648867</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3811188447251244</v>
+        <v>0.4069126020116725</v>
       </c>
       <c r="T88">
-        <v>7.744084173790402</v>
+        <v>8.339782956389664</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0890215448919205</v>
+        <v>0.0879983087437375</v>
       </c>
       <c r="W88">
-        <v>0.1829244737857024</v>
+        <v>0.1831299396042575</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3569428423894166</v>
+        <v>0.3528400510975842</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2122216857172215</v>
+        <v>0.2137716857172215</v>
       </c>
       <c r="C89">
-        <v>-7464.495255144138</v>
+        <v>-7631.728031309999</v>
       </c>
       <c r="D89">
-        <v>3524.965254223181</v>
+        <v>3492.437771268441</v>
       </c>
       <c r="E89">
-        <v>7915.231188255457</v>
+        <v>8049.936481466577</v>
       </c>
       <c r="F89">
-        <v>11719.36050936732</v>
+        <v>11854.06580257844</v>
       </c>
       <c r="G89">
         <v>729.9</v>
@@ -8591,37 +8591,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M89">
-        <v>2353.247590280958</v>
+        <v>2380.296413157751</v>
       </c>
       <c r="N89">
-        <v>-1522.927590280958</v>
+        <v>-1549.976413157751</v>
       </c>
       <c r="O89">
-        <v>-379.8181410160709</v>
+        <v>-386.5641174415431</v>
       </c>
       <c r="P89">
-        <v>-1143.109449264887</v>
+        <v>-1163.412295716208</v>
       </c>
       <c r="Q89">
-        <v>-566.0094492648867</v>
+        <v>-586.3122957162076</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4069126020116725</v>
+        <v>0.4370053188459786</v>
       </c>
       <c r="T89">
-        <v>8.339782956389664</v>
+        <v>9.034764869422139</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.0879983087437375</v>
+        <v>0.08699832796255864</v>
       </c>
       <c r="W89">
-        <v>0.1831299396042575</v>
+        <v>0.1833307357451182</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3528400510975842</v>
+        <v>0.3488305050623843</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2137716857172215</v>
+        <v>0.2153216857172215</v>
       </c>
       <c r="C90">
-        <v>-7631.728031309999</v>
+        <v>-7798.365985658618</v>
       </c>
       <c r="D90">
-        <v>3492.437771268441</v>
+        <v>3460.50511013094</v>
       </c>
       <c r="E90">
-        <v>8049.936481466577</v>
+        <v>8184.641774677695</v>
       </c>
       <c r="F90">
-        <v>11854.06580257844</v>
+        <v>11988.77109578956</v>
       </c>
       <c r="G90">
         <v>729.9</v>
@@ -8673,37 +8673,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M90">
-        <v>2380.296413157751</v>
+        <v>2407.345236034543</v>
       </c>
       <c r="N90">
-        <v>-1549.976413157751</v>
+        <v>-1577.025236034543</v>
       </c>
       <c r="O90">
-        <v>-386.5641174415431</v>
+        <v>-393.310093867015</v>
       </c>
       <c r="P90">
-        <v>-1163.412295716208</v>
+        <v>-1183.715142167528</v>
       </c>
       <c r="Q90">
-        <v>-586.3122957162076</v>
+        <v>-606.615142167528</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4370053188459786</v>
+        <v>0.4725694387410675</v>
       </c>
       <c r="T90">
-        <v>9.034764869422139</v>
+        <v>9.856107130278696</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08699832796255864</v>
+        <v>0.08602081865960856</v>
       </c>
       <c r="W90">
-        <v>0.1833307357451182</v>
+        <v>0.1835270196131506</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3488305050623843</v>
+        <v>0.3449110611852789</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2153216857172215</v>
+        <v>0.2168716857172214</v>
       </c>
       <c r="C91">
-        <v>-7798.365985658618</v>
+        <v>-7964.425286391293</v>
       </c>
       <c r="D91">
-        <v>3460.50511013094</v>
+        <v>3429.151102609384</v>
       </c>
       <c r="E91">
-        <v>8184.641774677695</v>
+        <v>8319.347067888813</v>
       </c>
       <c r="F91">
-        <v>11988.77109578956</v>
+        <v>12123.47638900068</v>
       </c>
       <c r="G91">
         <v>729.9</v>
@@ -8755,37 +8755,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M91">
-        <v>2407.345236034543</v>
+        <v>2434.394058911336</v>
       </c>
       <c r="N91">
-        <v>-1577.025236034543</v>
+        <v>-1604.074058911336</v>
       </c>
       <c r="O91">
-        <v>-393.310093867015</v>
+        <v>-400.0560702924871</v>
       </c>
       <c r="P91">
-        <v>-1183.715142167528</v>
+        <v>-1204.017988618848</v>
       </c>
       <c r="Q91">
-        <v>-606.615142167528</v>
+        <v>-626.9179886188484</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4725694387410675</v>
+        <v>0.5152463826151743</v>
       </c>
       <c r="T91">
-        <v>9.856107130278696</v>
+        <v>10.84171784330657</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08602081865960856</v>
+        <v>0.08506503178561292</v>
       </c>
       <c r="W91">
-        <v>0.1835270196131506</v>
+        <v>0.1837189416174489</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3449110611852789</v>
+        <v>0.341078716060998</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2168716857172214</v>
+        <v>0.2184216857172215</v>
       </c>
       <c r="C92">
-        <v>-7964.425286391293</v>
+        <v>-8129.921521000999</v>
       </c>
       <c r="D92">
-        <v>3429.151102609384</v>
+        <v>3398.360161210796</v>
       </c>
       <c r="E92">
-        <v>8319.347067888813</v>
+        <v>8454.052361099932</v>
       </c>
       <c r="F92">
-        <v>12123.47638900068</v>
+        <v>12258.18168221179</v>
       </c>
       <c r="G92">
         <v>729.9</v>
@@ -8837,37 +8837,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M92">
-        <v>2434.394058911336</v>
+        <v>2461.442881788128</v>
       </c>
       <c r="N92">
-        <v>-1604.074058911336</v>
+        <v>-1631.122881788128</v>
       </c>
       <c r="O92">
-        <v>-400.0560702924871</v>
+        <v>-406.8020467179592</v>
       </c>
       <c r="P92">
-        <v>-1204.017988618848</v>
+        <v>-1224.320835070169</v>
       </c>
       <c r="Q92">
-        <v>-626.9179886188484</v>
+        <v>-647.2208350701691</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5152463826151743</v>
+        <v>0.5674070917946381</v>
       </c>
       <c r="T92">
-        <v>10.84171784330657</v>
+        <v>12.04635315922952</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08506503178561292</v>
+        <v>0.08413025121654023</v>
       </c>
       <c r="W92">
-        <v>0.1837189416174489</v>
+        <v>0.1839066455557187</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.341078716060998</v>
+        <v>0.337330598302086</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2184216857172215</v>
+        <v>0.2199716857172215</v>
       </c>
       <c r="C93">
-        <v>-8129.921521000999</v>
+        <v>-8294.869722111793</v>
       </c>
       <c r="D93">
-        <v>3398.360161210796</v>
+        <v>3368.117253311122</v>
       </c>
       <c r="E93">
-        <v>8454.052361099932</v>
+        <v>8588.757654311052</v>
       </c>
       <c r="F93">
-        <v>12258.18168221179</v>
+        <v>12392.88697542291</v>
       </c>
       <c r="G93">
         <v>729.9</v>
@@ -8919,37 +8919,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M93">
-        <v>2461.442881788128</v>
+        <v>2488.491704664921</v>
       </c>
       <c r="N93">
-        <v>-1631.122881788128</v>
+        <v>-1658.171704664921</v>
       </c>
       <c r="O93">
-        <v>-406.8020467179592</v>
+        <v>-413.5480231434313</v>
       </c>
       <c r="P93">
-        <v>-1224.320835070169</v>
+        <v>-1244.62368152149</v>
       </c>
       <c r="Q93">
-        <v>-647.2208350701691</v>
+        <v>-667.5236815214897</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5674070917946381</v>
+        <v>0.6326079782689681</v>
       </c>
       <c r="T93">
-        <v>12.04635315922952</v>
+        <v>13.55214730413321</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08413025121654023</v>
+        <v>0.08321579196418655</v>
       </c>
       <c r="W93">
-        <v>0.1839066455557187</v>
+        <v>0.1840902689735913</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.337330598302086</v>
+        <v>0.3336639613640199</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2199716857172215</v>
+        <v>0.2215216857172215</v>
       </c>
       <c r="C94">
-        <v>-8294.869722111793</v>
+        <v>-8459.284391950639</v>
       </c>
       <c r="D94">
-        <v>3368.117253311122</v>
+        <v>3338.407876683394</v>
       </c>
       <c r="E94">
-        <v>8588.757654311052</v>
+        <v>8723.46294752217</v>
       </c>
       <c r="F94">
-        <v>12392.88697542291</v>
+        <v>12527.59226863403</v>
       </c>
       <c r="G94">
         <v>729.9</v>
@@ -9001,37 +9001,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M94">
-        <v>2488.491704664921</v>
+        <v>2515.540527541714</v>
       </c>
       <c r="N94">
-        <v>-1658.171704664921</v>
+        <v>-1685.220527541714</v>
       </c>
       <c r="O94">
-        <v>-413.5480231434313</v>
+        <v>-420.2939995689034</v>
       </c>
       <c r="P94">
-        <v>-1244.62368152149</v>
+        <v>-1264.92652797281</v>
       </c>
       <c r="Q94">
-        <v>-667.5236815214897</v>
+        <v>-687.8265279728101</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6326079782689681</v>
+        <v>0.7164376894502493</v>
       </c>
       <c r="T94">
-        <v>13.55214730413321</v>
+        <v>15.48816834758082</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08321579196418655</v>
+        <v>0.08232099850220603</v>
       </c>
       <c r="W94">
-        <v>0.1840902689735913</v>
+        <v>0.184269943500757</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3336639613640199</v>
+        <v>0.330076176833224</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2215216857172215</v>
+        <v>0.2230716857172215</v>
       </c>
       <c r="C95">
-        <v>-8459.284391950639</v>
+        <v>-8623.179525535441</v>
       </c>
       <c r="D95">
-        <v>3338.407876683394</v>
+        <v>3309.21803630971</v>
       </c>
       <c r="E95">
-        <v>8723.46294752217</v>
+        <v>8858.168240733288</v>
       </c>
       <c r="F95">
-        <v>12527.59226863403</v>
+        <v>12662.29756184515</v>
       </c>
       <c r="G95">
         <v>729.9</v>
@@ -9083,37 +9083,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M95">
-        <v>2515.540527541714</v>
+        <v>2542.589350418506</v>
       </c>
       <c r="N95">
-        <v>-1685.220527541714</v>
+        <v>-1712.269350418506</v>
       </c>
       <c r="O95">
-        <v>-420.2939995689034</v>
+        <v>-427.0399759943755</v>
       </c>
       <c r="P95">
-        <v>-1264.92652797281</v>
+        <v>-1285.229374424131</v>
       </c>
       <c r="Q95">
-        <v>-687.8265279728101</v>
+        <v>-708.1293744241308</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7164376894502493</v>
+        <v>0.8282106376919578</v>
       </c>
       <c r="T95">
-        <v>15.48816834758082</v>
+        <v>18.06952973884429</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08232099850220603</v>
+        <v>0.08144524319899107</v>
       </c>
       <c r="W95">
-        <v>0.184269943500757</v>
+        <v>0.1844457951656426</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.330076176833224</v>
+        <v>0.3265647281435088</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2230716857172215</v>
+        <v>0.2246216857172215</v>
       </c>
       <c r="C96">
-        <v>-8623.179525535441</v>
+        <v>-8786.568632657089</v>
       </c>
       <c r="D96">
-        <v>3309.21803630971</v>
+        <v>3280.534222399181</v>
       </c>
       <c r="E96">
-        <v>8858.168240733288</v>
+        <v>8992.873533944407</v>
       </c>
       <c r="F96">
-        <v>12662.29756184515</v>
+        <v>12797.00285505627</v>
       </c>
       <c r="G96">
         <v>729.9</v>
@@ -9165,37 +9165,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M96">
-        <v>2542.589350418506</v>
+        <v>2569.638173295299</v>
       </c>
       <c r="N96">
-        <v>-1712.269350418506</v>
+        <v>-1739.318173295299</v>
       </c>
       <c r="O96">
-        <v>-427.0399759943755</v>
+        <v>-433.7859524198476</v>
       </c>
       <c r="P96">
-        <v>-1285.229374424131</v>
+        <v>-1305.532220875451</v>
       </c>
       <c r="Q96">
-        <v>-708.1293744241308</v>
+        <v>-728.4322208754514</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8282106376919578</v>
+        <v>0.9846927652303497</v>
       </c>
       <c r="T96">
-        <v>18.06952973884429</v>
+        <v>21.68343568661316</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08144524319899107</v>
+        <v>0.08058792484952802</v>
       </c>
       <c r="W96">
-        <v>0.1844457951656426</v>
+        <v>0.1846179446902148</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3265647281435088</v>
+        <v>0.3231272046893666</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2246216857172215</v>
+        <v>0.2261716857172215</v>
       </c>
       <c r="C97">
-        <v>-8786.568632657089</v>
+        <v>-8949.464758728142</v>
       </c>
       <c r="D97">
-        <v>3280.534222399181</v>
+        <v>3252.343389539247</v>
       </c>
       <c r="E97">
-        <v>8992.873533944407</v>
+        <v>9127.578827155527</v>
       </c>
       <c r="F97">
-        <v>12797.00285505627</v>
+        <v>12931.70814826739</v>
       </c>
       <c r="G97">
         <v>729.9</v>
@@ -9247,37 +9247,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M97">
-        <v>2569.638173295299</v>
+        <v>2596.686996172092</v>
       </c>
       <c r="N97">
-        <v>-1739.318173295299</v>
+        <v>-1766.366996172092</v>
       </c>
       <c r="O97">
-        <v>-433.7859524198476</v>
+        <v>-440.5319288453197</v>
       </c>
       <c r="P97">
-        <v>-1305.532220875451</v>
+        <v>-1325.835067326772</v>
       </c>
       <c r="Q97">
-        <v>-728.4322208754514</v>
+        <v>-748.7350673267719</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9846927652303497</v>
+        <v>1.219415956537938</v>
       </c>
       <c r="T97">
-        <v>21.68343568661316</v>
+        <v>27.10429460826646</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08058792484952802</v>
+        <v>0.0797484672990121</v>
       </c>
       <c r="W97">
-        <v>0.1846179446902148</v>
+        <v>0.1847865077663584</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3231272046893666</v>
+        <v>0.3197612963071856</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2261716857172215</v>
+        <v>0.2277216857172215</v>
       </c>
       <c r="C98">
-        <v>-8949.46475872814</v>
+        <v>-9111.880504565679</v>
       </c>
       <c r="D98">
-        <v>3252.343389539247</v>
+        <v>3224.632936912827</v>
       </c>
       <c r="E98">
-        <v>9127.578827155525</v>
+        <v>9262.284120366643</v>
       </c>
       <c r="F98">
-        <v>12931.70814826739</v>
+        <v>13066.41344147851</v>
       </c>
       <c r="G98">
         <v>729.9</v>
@@ -9329,37 +9329,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M98">
-        <v>2596.686996172091</v>
+        <v>2623.735819048884</v>
       </c>
       <c r="N98">
-        <v>-1766.366996172091</v>
+        <v>-1793.415819048884</v>
       </c>
       <c r="O98">
-        <v>-440.5319288453196</v>
+        <v>-447.2779052707916</v>
       </c>
       <c r="P98">
-        <v>-1325.835067326772</v>
+        <v>-1346.137913778092</v>
       </c>
       <c r="Q98">
-        <v>-748.7350673267716</v>
+        <v>-769.0379137780923</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.219415956537935</v>
+        <v>1.610621275383913</v>
       </c>
       <c r="T98">
-        <v>27.10429460826639</v>
+        <v>36.13905947768852</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07974846729901211</v>
+        <v>0.07892631815159962</v>
       </c>
       <c r="W98">
-        <v>0.1847865077663584</v>
+        <v>0.1849515953151588</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3197612963071857</v>
+        <v>0.3164647880978333</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2277216857172215</v>
+        <v>0.2292716857172215</v>
       </c>
       <c r="C99">
-        <v>-9111.880504565679</v>
+        <v>-9273.828045171409</v>
       </c>
       <c r="D99">
-        <v>3224.632936912827</v>
+        <v>3197.390689518215</v>
       </c>
       <c r="E99">
-        <v>9262.284120366643</v>
+        <v>9396.989413577761</v>
       </c>
       <c r="F99">
-        <v>13066.41344147851</v>
+        <v>13201.11873468962</v>
       </c>
       <c r="G99">
         <v>729.9</v>
@@ -9411,37 +9411,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M99">
-        <v>2623.735819048884</v>
+        <v>2650.784641925677</v>
       </c>
       <c r="N99">
-        <v>-1793.415819048884</v>
+        <v>-1820.464641925676</v>
       </c>
       <c r="O99">
-        <v>-447.2779052707916</v>
+        <v>-454.0238816962637</v>
       </c>
       <c r="P99">
-        <v>-1346.137913778092</v>
+        <v>-1366.440760229413</v>
       </c>
       <c r="Q99">
-        <v>-769.0379137780923</v>
+        <v>-789.3407602294127</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.610621275383913</v>
+        <v>2.393031913075869</v>
       </c>
       <c r="T99">
-        <v>36.13905947768852</v>
+        <v>54.20858921653278</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07892631815159962</v>
+        <v>0.07812094755821596</v>
       </c>
       <c r="W99">
-        <v>0.1849515953151588</v>
+        <v>0.1851133137303102</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3164647880978333</v>
+        <v>0.3132355555662227</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2292716857172215</v>
+        <v>0.2308216857172214</v>
       </c>
       <c r="C100">
-        <v>-9273.828045171409</v>
+        <v>-9435.31914756777</v>
       </c>
       <c r="D100">
-        <v>3197.390689518215</v>
+        <v>3170.604880332974</v>
       </c>
       <c r="E100">
-        <v>9396.989413577761</v>
+        <v>9531.694706788881</v>
       </c>
       <c r="F100">
-        <v>13201.11873468962</v>
+        <v>13335.82402790074</v>
       </c>
       <c r="G100">
         <v>729.9</v>
@@ -9493,37 +9493,37 @@
         <v>830.3200000000001</v>
       </c>
       <c r="M100">
-        <v>2650.784641925677</v>
+        <v>2677.833464802469</v>
       </c>
       <c r="N100">
-        <v>-1820.464641925676</v>
+        <v>-1847.513464802469</v>
       </c>
       <c r="O100">
-        <v>-454.0238816962637</v>
+        <v>-460.7698581217358</v>
       </c>
       <c r="P100">
-        <v>-1366.440760229413</v>
+        <v>-1386.743606680733</v>
       </c>
       <c r="Q100">
-        <v>-789.3407602294127</v>
+        <v>-809.6436066807333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.393031913075869</v>
+        <v>4.740263826151739</v>
       </c>
       <c r="T100">
-        <v>54.20858921653278</v>
+        <v>108.4171784330656</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07812094755821596</v>
+        <v>0.07733184707782993</v>
       </c>
       <c r="W100">
-        <v>0.1851133137303102</v>
+        <v>0.1852717651067718</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3132355555662227</v>
+        <v>0.3100715600554528</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2308216857172214</v>
-      </c>
-      <c r="C101">
-        <v>-9435.31914756777</v>
-      </c>
-      <c r="D101">
-        <v>3170.604880332974</v>
-      </c>
-      <c r="E101">
-        <v>9531.694706788881</v>
-      </c>
-      <c r="F101">
-        <v>13335.82402790074</v>
-      </c>
-      <c r="G101">
-        <v>729.9</v>
-      </c>
-      <c r="H101">
-        <v>9666.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1407.42</v>
-      </c>
-      <c r="K101">
-        <v>577.1</v>
-      </c>
-      <c r="L101">
-        <v>830.3200000000001</v>
-      </c>
-      <c r="M101">
-        <v>2677.833464802469</v>
-      </c>
-      <c r="N101">
-        <v>-1847.513464802469</v>
-      </c>
-      <c r="O101">
-        <v>-460.7698581217358</v>
-      </c>
-      <c r="P101">
-        <v>-1386.743606680733</v>
-      </c>
-      <c r="Q101">
-        <v>-809.6436066807333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.740263826151739</v>
-      </c>
-      <c r="T101">
-        <v>108.4171784330656</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07733184707782993</v>
-      </c>
-      <c r="W101">
-        <v>0.1852717651067718</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3100715600554528</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
